--- a/output/version3/test/20-15/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/CTDE/RL-RL with CL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1092</v>
+        <v>799</v>
       </c>
       <c r="C2" t="n">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D2" t="n">
-        <v>881</v>
+        <v>1024</v>
       </c>
       <c r="E2" t="n">
-        <v>920</v>
+        <v>880</v>
       </c>
       <c r="F2" t="n">
-        <v>901</v>
+        <v>1094</v>
       </c>
       <c r="G2" t="n">
-        <v>1035</v>
+        <v>1023</v>
       </c>
       <c r="H2" t="n">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="I2" t="n">
-        <v>964</v>
+        <v>893</v>
       </c>
       <c r="J2" t="n">
-        <v>1058</v>
+        <v>925</v>
       </c>
       <c r="K2" t="n">
-        <v>997</v>
+        <v>1056</v>
       </c>
       <c r="L2" t="n">
-        <v>987.9</v>
+        <v>972.1</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="C3" t="n">
-        <v>998</v>
+        <v>1048</v>
       </c>
       <c r="D3" t="n">
-        <v>1088</v>
+        <v>999</v>
       </c>
       <c r="E3" t="n">
-        <v>984</v>
+        <v>1013</v>
       </c>
       <c r="F3" t="n">
-        <v>1120</v>
+        <v>884</v>
       </c>
       <c r="G3" t="n">
-        <v>1064</v>
+        <v>928</v>
       </c>
       <c r="H3" t="n">
-        <v>891</v>
+        <v>1023</v>
       </c>
       <c r="I3" t="n">
-        <v>1141</v>
+        <v>1028</v>
       </c>
       <c r="J3" t="n">
-        <v>1040</v>
+        <v>992</v>
       </c>
       <c r="K3" t="n">
-        <v>1151</v>
+        <v>956</v>
       </c>
       <c r="L3" t="n">
-        <v>1056.2</v>
+        <v>996</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>951</v>
+        <v>846</v>
       </c>
       <c r="C4" t="n">
-        <v>924</v>
+        <v>848</v>
       </c>
       <c r="D4" t="n">
-        <v>1055</v>
+        <v>868</v>
       </c>
       <c r="E4" t="n">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="F4" t="n">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="G4" t="n">
-        <v>1034</v>
+        <v>817</v>
       </c>
       <c r="H4" t="n">
-        <v>1141</v>
+        <v>817</v>
       </c>
       <c r="I4" t="n">
-        <v>956</v>
+        <v>885</v>
       </c>
       <c r="J4" t="n">
-        <v>925</v>
+        <v>976</v>
       </c>
       <c r="K4" t="n">
-        <v>1152</v>
+        <v>895</v>
       </c>
       <c r="L4" t="n">
-        <v>1001.8</v>
+        <v>879.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1135</v>
+        <v>1019</v>
       </c>
       <c r="C5" t="n">
-        <v>946</v>
+        <v>1032</v>
       </c>
       <c r="D5" t="n">
-        <v>1108</v>
+        <v>1097</v>
       </c>
       <c r="E5" t="n">
-        <v>868</v>
+        <v>1037</v>
       </c>
       <c r="F5" t="n">
-        <v>1090</v>
+        <v>1017</v>
       </c>
       <c r="G5" t="n">
-        <v>1098</v>
+        <v>812</v>
       </c>
       <c r="H5" t="n">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="I5" t="n">
-        <v>867</v>
+        <v>1051</v>
       </c>
       <c r="J5" t="n">
-        <v>1054</v>
+        <v>815</v>
       </c>
       <c r="K5" t="n">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="L5" t="n">
-        <v>996.8</v>
+        <v>970</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1027</v>
       </c>
       <c r="C6" t="n">
-        <v>1006</v>
+        <v>967</v>
       </c>
       <c r="D6" t="n">
-        <v>916</v>
+        <v>813</v>
       </c>
       <c r="E6" t="n">
-        <v>890</v>
+        <v>768</v>
       </c>
       <c r="F6" t="n">
-        <v>1095</v>
+        <v>974</v>
       </c>
       <c r="G6" t="n">
-        <v>985</v>
+        <v>969</v>
       </c>
       <c r="H6" t="n">
-        <v>941</v>
+        <v>760</v>
       </c>
       <c r="I6" t="n">
-        <v>1015</v>
+        <v>799</v>
       </c>
       <c r="J6" t="n">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="K6" t="n">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="L6" t="n">
-        <v>951.2</v>
+        <v>880.6</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>1211</v>
+        <v>1006</v>
       </c>
       <c r="C7" t="n">
-        <v>855</v>
+        <v>927</v>
       </c>
       <c r="D7" t="n">
-        <v>972</v>
+        <v>871</v>
       </c>
       <c r="E7" t="n">
-        <v>956</v>
+        <v>866</v>
       </c>
       <c r="F7" t="n">
-        <v>932</v>
+        <v>924</v>
       </c>
       <c r="G7" t="n">
-        <v>978</v>
+        <v>1201</v>
       </c>
       <c r="H7" t="n">
-        <v>811</v>
+        <v>847</v>
       </c>
       <c r="I7" t="n">
-        <v>980</v>
+        <v>910</v>
       </c>
       <c r="J7" t="n">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="K7" t="n">
-        <v>977</v>
+        <v>970</v>
       </c>
       <c r="L7" t="n">
-        <v>966.8</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>762</v>
+        <v>857</v>
       </c>
       <c r="C8" t="n">
-        <v>1080</v>
+        <v>916</v>
       </c>
       <c r="D8" t="n">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="E8" t="n">
-        <v>940</v>
+        <v>1014</v>
       </c>
       <c r="F8" t="n">
-        <v>876</v>
+        <v>881</v>
       </c>
       <c r="G8" t="n">
-        <v>905</v>
+        <v>1040</v>
       </c>
       <c r="H8" t="n">
-        <v>817</v>
+        <v>892</v>
       </c>
       <c r="I8" t="n">
-        <v>940</v>
+        <v>1005</v>
       </c>
       <c r="J8" t="n">
-        <v>1031</v>
+        <v>873</v>
       </c>
       <c r="K8" t="n">
-        <v>1039</v>
+        <v>830</v>
       </c>
       <c r="L8" t="n">
-        <v>932.2</v>
+        <v>922.2</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1236</v>
+        <v>1109</v>
       </c>
       <c r="C9" t="n">
-        <v>1269</v>
+        <v>870</v>
       </c>
       <c r="D9" t="n">
-        <v>834</v>
+        <v>891</v>
       </c>
       <c r="E9" t="n">
+        <v>793</v>
+      </c>
+      <c r="F9" t="n">
+        <v>956</v>
+      </c>
+      <c r="G9" t="n">
+        <v>731</v>
+      </c>
+      <c r="H9" t="n">
+        <v>849</v>
+      </c>
+      <c r="I9" t="n">
+        <v>858</v>
+      </c>
+      <c r="J9" t="n">
+        <v>959</v>
+      </c>
+      <c r="K9" t="n">
         <v>905</v>
       </c>
-      <c r="F9" t="n">
-        <v>941</v>
-      </c>
-      <c r="G9" t="n">
-        <v>857</v>
-      </c>
-      <c r="H9" t="n">
-        <v>972</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1133</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1161</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1091</v>
-      </c>
       <c r="L9" t="n">
-        <v>1039.9</v>
+        <v>892.1</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>902</v>
+        <v>961</v>
       </c>
       <c r="C10" t="n">
-        <v>886</v>
+        <v>850</v>
       </c>
       <c r="D10" t="n">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="E10" t="n">
-        <v>1093</v>
+        <v>997</v>
       </c>
       <c r="F10" t="n">
-        <v>847</v>
+        <v>828</v>
       </c>
       <c r="G10" t="n">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="H10" t="n">
-        <v>970</v>
+        <v>826</v>
       </c>
       <c r="I10" t="n">
-        <v>1063</v>
+        <v>912</v>
       </c>
       <c r="J10" t="n">
-        <v>862</v>
+        <v>948</v>
       </c>
       <c r="K10" t="n">
-        <v>1065</v>
+        <v>903</v>
       </c>
       <c r="L10" t="n">
-        <v>940.6</v>
+        <v>895.5</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1063</v>
+        <v>921</v>
       </c>
       <c r="C11" t="n">
-        <v>1006</v>
+        <v>909</v>
       </c>
       <c r="D11" t="n">
-        <v>1070</v>
+        <v>954</v>
       </c>
       <c r="E11" t="n">
-        <v>907</v>
+        <v>835</v>
       </c>
       <c r="F11" t="n">
-        <v>1017</v>
+        <v>938</v>
       </c>
       <c r="G11" t="n">
-        <v>1144</v>
+        <v>841</v>
       </c>
       <c r="H11" t="n">
-        <v>947</v>
+        <v>919</v>
       </c>
       <c r="I11" t="n">
-        <v>1080</v>
+        <v>956</v>
       </c>
       <c r="J11" t="n">
-        <v>1144</v>
+        <v>908</v>
       </c>
       <c r="K11" t="n">
-        <v>986</v>
+        <v>1004</v>
       </c>
       <c r="L11" t="n">
-        <v>1036.4</v>
+        <v>918.5</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>955</v>
+        <v>1029</v>
       </c>
       <c r="C12" t="n">
-        <v>1023</v>
+        <v>1041</v>
       </c>
       <c r="D12" t="n">
-        <v>1150</v>
+        <v>948</v>
       </c>
       <c r="E12" t="n">
-        <v>1071</v>
+        <v>873</v>
       </c>
       <c r="F12" t="n">
-        <v>1020</v>
+        <v>926</v>
       </c>
       <c r="G12" t="n">
-        <v>1037</v>
+        <v>897</v>
       </c>
       <c r="H12" t="n">
-        <v>1261</v>
+        <v>841</v>
       </c>
       <c r="I12" t="n">
-        <v>959</v>
+        <v>836</v>
       </c>
       <c r="J12" t="n">
-        <v>937</v>
+        <v>983</v>
       </c>
       <c r="K12" t="n">
-        <v>1119</v>
+        <v>809</v>
       </c>
       <c r="L12" t="n">
-        <v>1053.2</v>
+        <v>918.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>881</v>
+        <v>758</v>
       </c>
       <c r="C13" t="n">
-        <v>874</v>
+        <v>950</v>
       </c>
       <c r="D13" t="n">
-        <v>952</v>
+        <v>850</v>
       </c>
       <c r="E13" t="n">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="F13" t="n">
-        <v>1021</v>
+        <v>868</v>
       </c>
       <c r="G13" t="n">
-        <v>811</v>
+        <v>906</v>
       </c>
       <c r="H13" t="n">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="I13" t="n">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="J13" t="n">
-        <v>871</v>
+        <v>735</v>
       </c>
       <c r="K13" t="n">
-        <v>1029</v>
+        <v>802</v>
       </c>
       <c r="L13" t="n">
-        <v>904.6</v>
+        <v>846.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>979</v>
+        <v>890</v>
       </c>
       <c r="C14" t="n">
-        <v>968</v>
+        <v>788</v>
       </c>
       <c r="D14" t="n">
-        <v>1031</v>
+        <v>999</v>
       </c>
       <c r="E14" t="n">
-        <v>1138</v>
+        <v>922</v>
       </c>
       <c r="F14" t="n">
-        <v>1024</v>
+        <v>942</v>
       </c>
       <c r="G14" t="n">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="H14" t="n">
-        <v>957</v>
+        <v>900</v>
       </c>
       <c r="I14" t="n">
-        <v>1253</v>
+        <v>937</v>
       </c>
       <c r="J14" t="n">
+        <v>889</v>
+      </c>
+      <c r="K14" t="n">
         <v>1175</v>
       </c>
-      <c r="K14" t="n">
-        <v>917</v>
-      </c>
       <c r="L14" t="n">
-        <v>1036</v>
+        <v>937.1</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>1165</v>
+        <v>1084</v>
       </c>
       <c r="C15" t="n">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="D15" t="n">
-        <v>871</v>
+        <v>958</v>
       </c>
       <c r="E15" t="n">
-        <v>951</v>
+        <v>1044</v>
       </c>
       <c r="F15" t="n">
-        <v>1075</v>
+        <v>928</v>
       </c>
       <c r="G15" t="n">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="H15" t="n">
-        <v>935</v>
+        <v>1045</v>
       </c>
       <c r="I15" t="n">
-        <v>834</v>
+        <v>881</v>
       </c>
       <c r="J15" t="n">
-        <v>929</v>
+        <v>817</v>
       </c>
       <c r="K15" t="n">
-        <v>907</v>
+        <v>890</v>
       </c>
       <c r="L15" t="n">
-        <v>955.7</v>
+        <v>955.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1213</v>
+        <v>855</v>
       </c>
       <c r="C16" t="n">
-        <v>1016</v>
+        <v>1136</v>
       </c>
       <c r="D16" t="n">
-        <v>1008</v>
+        <v>768</v>
       </c>
       <c r="E16" t="n">
-        <v>921</v>
+        <v>1086</v>
       </c>
       <c r="F16" t="n">
-        <v>902</v>
+        <v>977</v>
       </c>
       <c r="G16" t="n">
-        <v>952</v>
+        <v>917</v>
       </c>
       <c r="H16" t="n">
-        <v>998</v>
+        <v>1091</v>
       </c>
       <c r="I16" t="n">
-        <v>875</v>
+        <v>956</v>
       </c>
       <c r="J16" t="n">
-        <v>915</v>
+        <v>957</v>
       </c>
       <c r="K16" t="n">
-        <v>1005</v>
+        <v>992</v>
       </c>
       <c r="L16" t="n">
-        <v>980.5</v>
+        <v>973.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>984</v>
+        <v>952</v>
       </c>
       <c r="C17" t="n">
-        <v>1138</v>
+        <v>991</v>
       </c>
       <c r="D17" t="n">
-        <v>969</v>
+        <v>852</v>
       </c>
       <c r="E17" t="n">
-        <v>1014</v>
+        <v>1034</v>
       </c>
       <c r="F17" t="n">
-        <v>855</v>
+        <v>959</v>
       </c>
       <c r="G17" t="n">
-        <v>1178</v>
+        <v>1205</v>
       </c>
       <c r="H17" t="n">
-        <v>1072</v>
+        <v>906</v>
       </c>
       <c r="I17" t="n">
-        <v>980</v>
+        <v>930</v>
       </c>
       <c r="J17" t="n">
-        <v>1149</v>
+        <v>967</v>
       </c>
       <c r="K17" t="n">
-        <v>1014</v>
+        <v>759</v>
       </c>
       <c r="L17" t="n">
-        <v>1035.3</v>
+        <v>955.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>997</v>
+        <v>1056</v>
       </c>
       <c r="C18" t="n">
-        <v>1036</v>
+        <v>957</v>
       </c>
       <c r="D18" t="n">
-        <v>1012</v>
+        <v>962</v>
       </c>
       <c r="E18" t="n">
-        <v>978</v>
+        <v>1039</v>
       </c>
       <c r="F18" t="n">
-        <v>931</v>
+        <v>1000</v>
       </c>
       <c r="G18" t="n">
-        <v>1108</v>
+        <v>918</v>
       </c>
       <c r="H18" t="n">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="I18" t="n">
-        <v>849</v>
+        <v>1018</v>
       </c>
       <c r="J18" t="n">
-        <v>974</v>
+        <v>833</v>
       </c>
       <c r="K18" t="n">
-        <v>935</v>
+        <v>964</v>
       </c>
       <c r="L18" t="n">
-        <v>981.4</v>
+        <v>974.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>989</v>
+        <v>879</v>
       </c>
       <c r="C19" t="n">
-        <v>876</v>
+        <v>818</v>
       </c>
       <c r="D19" t="n">
-        <v>915</v>
+        <v>1034</v>
       </c>
       <c r="E19" t="n">
-        <v>1064</v>
+        <v>922</v>
       </c>
       <c r="F19" t="n">
-        <v>908</v>
+        <v>980</v>
       </c>
       <c r="G19" t="n">
-        <v>884</v>
+        <v>900</v>
       </c>
       <c r="H19" t="n">
-        <v>837</v>
+        <v>784</v>
       </c>
       <c r="I19" t="n">
-        <v>901</v>
+        <v>794</v>
       </c>
       <c r="J19" t="n">
-        <v>1125</v>
+        <v>1071</v>
       </c>
       <c r="K19" t="n">
-        <v>863</v>
+        <v>969</v>
       </c>
       <c r="L19" t="n">
-        <v>936.2</v>
+        <v>915.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>960</v>
+        <v>1006</v>
       </c>
       <c r="C20" t="n">
-        <v>1265</v>
+        <v>1112</v>
       </c>
       <c r="D20" t="n">
-        <v>1005</v>
+        <v>975</v>
       </c>
       <c r="E20" t="n">
-        <v>1097</v>
+        <v>1033</v>
       </c>
       <c r="F20" t="n">
-        <v>1192</v>
+        <v>1022</v>
       </c>
       <c r="G20" t="n">
-        <v>1043</v>
+        <v>1157</v>
       </c>
       <c r="H20" t="n">
-        <v>1107</v>
+        <v>1039</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>1147</v>
       </c>
       <c r="J20" t="n">
-        <v>1071</v>
+        <v>1161</v>
       </c>
       <c r="K20" t="n">
-        <v>1145</v>
+        <v>957</v>
       </c>
       <c r="L20" t="n">
-        <v>1088.5</v>
+        <v>1060.9</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>871</v>
+        <v>899</v>
       </c>
       <c r="C21" t="n">
-        <v>871</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="E21" t="n">
-        <v>1011</v>
+        <v>990</v>
       </c>
       <c r="F21" t="n">
-        <v>1083</v>
+        <v>974</v>
       </c>
       <c r="G21" t="n">
-        <v>1078</v>
+        <v>992</v>
       </c>
       <c r="H21" t="n">
-        <v>976</v>
+        <v>953</v>
       </c>
       <c r="I21" t="n">
-        <v>929</v>
+        <v>1134</v>
       </c>
       <c r="J21" t="n">
-        <v>873</v>
+        <v>953</v>
       </c>
       <c r="K21" t="n">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="L21" t="n">
-        <v>949.4</v>
+        <v>968.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>916</v>
+        <v>867</v>
       </c>
       <c r="C22" t="n">
-        <v>836</v>
+        <v>925</v>
       </c>
       <c r="D22" t="n">
-        <v>954</v>
+        <v>868</v>
       </c>
       <c r="E22" t="n">
-        <v>971</v>
+        <v>887</v>
       </c>
       <c r="F22" t="n">
-        <v>881</v>
+        <v>808</v>
       </c>
       <c r="G22" t="n">
-        <v>1012</v>
+        <v>907</v>
       </c>
       <c r="H22" t="n">
-        <v>1063</v>
+        <v>927</v>
       </c>
       <c r="I22" t="n">
-        <v>1166</v>
+        <v>886</v>
       </c>
       <c r="J22" t="n">
-        <v>947</v>
+        <v>906</v>
       </c>
       <c r="K22" t="n">
-        <v>854</v>
+        <v>837</v>
       </c>
       <c r="L22" t="n">
-        <v>960</v>
+        <v>881.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>1272</v>
+        <v>975</v>
       </c>
       <c r="C23" t="n">
-        <v>1123</v>
+        <v>956</v>
       </c>
       <c r="D23" t="n">
-        <v>1180</v>
+        <v>1072</v>
       </c>
       <c r="E23" t="n">
-        <v>1144</v>
+        <v>1007</v>
       </c>
       <c r="F23" t="n">
-        <v>1114</v>
+        <v>991</v>
       </c>
       <c r="G23" t="n">
-        <v>1048</v>
+        <v>1035</v>
       </c>
       <c r="H23" t="n">
-        <v>980</v>
+        <v>1008</v>
       </c>
       <c r="I23" t="n">
-        <v>1140</v>
+        <v>1101</v>
       </c>
       <c r="J23" t="n">
-        <v>1183</v>
+        <v>981</v>
       </c>
       <c r="K23" t="n">
-        <v>1200</v>
+        <v>1030</v>
       </c>
       <c r="L23" t="n">
-        <v>1138.4</v>
+        <v>1015.6</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="C24" t="n">
-        <v>1050</v>
+        <v>931</v>
       </c>
       <c r="D24" t="n">
-        <v>1133</v>
+        <v>1052</v>
       </c>
       <c r="E24" t="n">
-        <v>1032</v>
+        <v>1008</v>
       </c>
       <c r="F24" t="n">
-        <v>978</v>
+        <v>1037</v>
       </c>
       <c r="G24" t="n">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="H24" t="n">
-        <v>1293</v>
+        <v>1193</v>
       </c>
       <c r="I24" t="n">
-        <v>968</v>
+        <v>1031</v>
       </c>
       <c r="J24" t="n">
-        <v>1135</v>
+        <v>1076</v>
       </c>
       <c r="K24" t="n">
-        <v>1103</v>
+        <v>924</v>
       </c>
       <c r="L24" t="n">
-        <v>1083.2</v>
+        <v>1038.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1032</v>
+        <v>1089</v>
       </c>
       <c r="C25" t="n">
+        <v>923</v>
+      </c>
+      <c r="D25" t="n">
+        <v>949</v>
+      </c>
+      <c r="E25" t="n">
+        <v>883</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>977</v>
+      </c>
+      <c r="H25" t="n">
+        <v>824</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1155</v>
+      </c>
+      <c r="J25" t="n">
         <v>973</v>
       </c>
-      <c r="D25" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E25" t="n">
-        <v>999</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1055</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1072</v>
-      </c>
-      <c r="H25" t="n">
-        <v>954</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1025</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1005</v>
-      </c>
       <c r="K25" t="n">
-        <v>973</v>
+        <v>895</v>
       </c>
       <c r="L25" t="n">
-        <v>1010.6</v>
+        <v>966.8</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1103</v>
+        <v>838</v>
       </c>
       <c r="C26" t="n">
-        <v>1066</v>
+        <v>996</v>
       </c>
       <c r="D26" t="n">
+        <v>909</v>
+      </c>
+      <c r="E26" t="n">
+        <v>909</v>
+      </c>
+      <c r="F26" t="n">
+        <v>837</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1003</v>
+      </c>
+      <c r="H26" t="n">
+        <v>943</v>
+      </c>
+      <c r="I26" t="n">
         <v>861</v>
       </c>
-      <c r="E26" t="n">
-        <v>953</v>
-      </c>
-      <c r="F26" t="n">
-        <v>763</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1146</v>
-      </c>
-      <c r="H26" t="n">
-        <v>848</v>
-      </c>
-      <c r="I26" t="n">
-        <v>921</v>
-      </c>
       <c r="J26" t="n">
-        <v>848</v>
+        <v>751</v>
       </c>
       <c r="K26" t="n">
-        <v>1120</v>
+        <v>992</v>
       </c>
       <c r="L26" t="n">
-        <v>962.9</v>
+        <v>903.9</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1218</v>
+        <v>949</v>
       </c>
       <c r="C27" t="n">
-        <v>1279</v>
+        <v>1213</v>
       </c>
       <c r="D27" t="n">
+        <v>1037</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1009</v>
+      </c>
+      <c r="F27" t="n">
+        <v>922</v>
+      </c>
+      <c r="G27" t="n">
+        <v>988</v>
+      </c>
+      <c r="H27" t="n">
+        <v>954</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1212</v>
+      </c>
+      <c r="J27" t="n">
+        <v>892</v>
+      </c>
+      <c r="K27" t="n">
         <v>1060</v>
       </c>
-      <c r="E27" t="n">
-        <v>994</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1078</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1094</v>
-      </c>
-      <c r="H27" t="n">
-        <v>1055</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1230</v>
-      </c>
-      <c r="J27" t="n">
-        <v>984</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1004</v>
-      </c>
       <c r="L27" t="n">
-        <v>1099.6</v>
+        <v>1023.6</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1294</v>
+        <v>916</v>
       </c>
       <c r="C28" t="n">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="D28" t="n">
+        <v>1033</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1098</v>
+      </c>
+      <c r="F28" t="n">
+        <v>947</v>
+      </c>
+      <c r="G28" t="n">
+        <v>939</v>
+      </c>
+      <c r="H28" t="n">
         <v>1115</v>
       </c>
-      <c r="E28" t="n">
-        <v>1161</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1204</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1069</v>
-      </c>
-      <c r="H28" t="n">
-        <v>997</v>
-      </c>
       <c r="I28" t="n">
-        <v>1141</v>
+        <v>1169</v>
       </c>
       <c r="J28" t="n">
-        <v>1084</v>
+        <v>1101</v>
       </c>
       <c r="K28" t="n">
-        <v>1055</v>
+        <v>1042</v>
       </c>
       <c r="L28" t="n">
-        <v>1105.1</v>
+        <v>1028.9</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1055</v>
+        <v>861</v>
       </c>
       <c r="C29" t="n">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D29" t="n">
-        <v>908</v>
+        <v>1111</v>
       </c>
       <c r="E29" t="n">
-        <v>1009</v>
+        <v>948</v>
       </c>
       <c r="F29" t="n">
-        <v>1228</v>
+        <v>978</v>
       </c>
       <c r="G29" t="n">
-        <v>1091</v>
+        <v>1070</v>
       </c>
       <c r="H29" t="n">
-        <v>1148</v>
+        <v>922</v>
       </c>
       <c r="I29" t="n">
-        <v>962</v>
+        <v>897</v>
       </c>
       <c r="J29" t="n">
-        <v>995</v>
+        <v>838</v>
       </c>
       <c r="K29" t="n">
-        <v>927</v>
+        <v>1008</v>
       </c>
       <c r="L29" t="n">
-        <v>1030.3</v>
+        <v>963.4</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1251</v>
+        <v>1041</v>
       </c>
       <c r="C30" t="n">
-        <v>1057</v>
+        <v>952</v>
       </c>
       <c r="D30" t="n">
-        <v>952</v>
+        <v>977</v>
       </c>
       <c r="E30" t="n">
-        <v>1017</v>
+        <v>944</v>
       </c>
       <c r="F30" t="n">
-        <v>1002</v>
+        <v>908</v>
       </c>
       <c r="G30" t="n">
-        <v>977</v>
+        <v>1037</v>
       </c>
       <c r="H30" t="n">
-        <v>1210</v>
+        <v>927</v>
       </c>
       <c r="I30" t="n">
-        <v>931</v>
+        <v>972</v>
       </c>
       <c r="J30" t="n">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="K30" t="n">
-        <v>939</v>
+        <v>979</v>
       </c>
       <c r="L30" t="n">
-        <v>1030.3</v>
+        <v>970.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>902</v>
+        <v>944</v>
       </c>
       <c r="C31" t="n">
-        <v>867</v>
+        <v>943</v>
       </c>
       <c r="D31" t="n">
-        <v>918</v>
+        <v>899</v>
       </c>
       <c r="E31" t="n">
-        <v>886</v>
+        <v>965</v>
       </c>
       <c r="F31" t="n">
-        <v>1091</v>
+        <v>944</v>
       </c>
       <c r="G31" t="n">
-        <v>927</v>
+        <v>974</v>
       </c>
       <c r="H31" t="n">
-        <v>1058</v>
+        <v>778</v>
       </c>
       <c r="I31" t="n">
-        <v>962</v>
+        <v>888</v>
       </c>
       <c r="J31" t="n">
-        <v>1122</v>
+        <v>839</v>
       </c>
       <c r="K31" t="n">
-        <v>954</v>
+        <v>856</v>
       </c>
       <c r="L31" t="n">
-        <v>968.7</v>
+        <v>903</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1007</v>
+        <v>865</v>
       </c>
       <c r="C32" t="n">
-        <v>1180</v>
+        <v>1019</v>
       </c>
       <c r="D32" t="n">
-        <v>1170</v>
+        <v>937</v>
       </c>
       <c r="E32" t="n">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="F32" t="n">
-        <v>881</v>
+        <v>995</v>
       </c>
       <c r="G32" t="n">
-        <v>1100</v>
+        <v>935</v>
       </c>
       <c r="H32" t="n">
-        <v>1190</v>
+        <v>850</v>
       </c>
       <c r="I32" t="n">
-        <v>1025</v>
+        <v>1088</v>
       </c>
       <c r="J32" t="n">
-        <v>951</v>
+        <v>873</v>
       </c>
       <c r="K32" t="n">
-        <v>1051</v>
+        <v>986</v>
       </c>
       <c r="L32" t="n">
-        <v>1047.7</v>
+        <v>947.3</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1007</v>
+        <v>919</v>
       </c>
       <c r="C33" t="n">
-        <v>936</v>
+        <v>899</v>
       </c>
       <c r="D33" t="n">
-        <v>1067</v>
+        <v>884</v>
       </c>
       <c r="E33" t="n">
-        <v>1019</v>
+        <v>988</v>
       </c>
       <c r="F33" t="n">
-        <v>1175</v>
+        <v>1022</v>
       </c>
       <c r="G33" t="n">
-        <v>1002</v>
+        <v>911</v>
       </c>
       <c r="H33" t="n">
-        <v>1194</v>
+        <v>794</v>
       </c>
       <c r="I33" t="n">
-        <v>969</v>
+        <v>930</v>
       </c>
       <c r="J33" t="n">
-        <v>1130</v>
+        <v>1057</v>
       </c>
       <c r="K33" t="n">
-        <v>1037</v>
+        <v>918</v>
       </c>
       <c r="L33" t="n">
-        <v>1053.6</v>
+        <v>932.2</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>1059</v>
+        <v>879</v>
       </c>
       <c r="C34" t="n">
-        <v>821</v>
+        <v>776</v>
       </c>
       <c r="D34" t="n">
-        <v>1049</v>
+        <v>918</v>
       </c>
       <c r="E34" t="n">
-        <v>1094</v>
+        <v>849</v>
       </c>
       <c r="F34" t="n">
-        <v>919</v>
+        <v>944</v>
       </c>
       <c r="G34" t="n">
-        <v>992</v>
+        <v>856</v>
       </c>
       <c r="H34" t="n">
-        <v>807</v>
+        <v>1058</v>
       </c>
       <c r="I34" t="n">
-        <v>918</v>
+        <v>837</v>
       </c>
       <c r="J34" t="n">
-        <v>915</v>
+        <v>887</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="L34" t="n">
-        <v>957.4</v>
+        <v>900.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>967</v>
+        <v>912</v>
       </c>
       <c r="C35" t="n">
-        <v>883</v>
+        <v>971</v>
       </c>
       <c r="D35" t="n">
-        <v>1031</v>
+        <v>926</v>
       </c>
       <c r="E35" t="n">
-        <v>861</v>
+        <v>933</v>
       </c>
       <c r="F35" t="n">
-        <v>827</v>
+        <v>907</v>
       </c>
       <c r="G35" t="n">
-        <v>1012</v>
+        <v>864</v>
       </c>
       <c r="H35" t="n">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="I35" t="n">
-        <v>807</v>
+        <v>979</v>
       </c>
       <c r="J35" t="n">
-        <v>961</v>
+        <v>1019</v>
       </c>
       <c r="K35" t="n">
-        <v>1142</v>
+        <v>857</v>
       </c>
       <c r="L35" t="n">
-        <v>940.7</v>
+        <v>926.9</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1168</v>
+        <v>1086</v>
       </c>
       <c r="C36" t="n">
-        <v>1176</v>
+        <v>941</v>
       </c>
       <c r="D36" t="n">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="E36" t="n">
-        <v>1155</v>
+        <v>1009</v>
       </c>
       <c r="F36" t="n">
-        <v>1045</v>
+        <v>1104</v>
       </c>
       <c r="G36" t="n">
-        <v>1058</v>
+        <v>962</v>
       </c>
       <c r="H36" t="n">
-        <v>1080</v>
+        <v>974</v>
       </c>
       <c r="I36" t="n">
-        <v>1231</v>
+        <v>981</v>
       </c>
       <c r="J36" t="n">
-        <v>986</v>
+        <v>1014</v>
       </c>
       <c r="K36" t="n">
-        <v>957</v>
+        <v>976</v>
       </c>
       <c r="L36" t="n">
-        <v>1090</v>
+        <v>1009.5</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>959</v>
+        <v>918</v>
       </c>
       <c r="C37" t="n">
-        <v>823</v>
+        <v>956</v>
       </c>
       <c r="D37" t="n">
-        <v>832</v>
+        <v>943</v>
       </c>
       <c r="E37" t="n">
-        <v>1158</v>
+        <v>877</v>
       </c>
       <c r="F37" t="n">
-        <v>971</v>
+        <v>870</v>
       </c>
       <c r="G37" t="n">
-        <v>885</v>
+        <v>841</v>
       </c>
       <c r="H37" t="n">
-        <v>959</v>
+        <v>867</v>
       </c>
       <c r="I37" t="n">
-        <v>919</v>
+        <v>834</v>
       </c>
       <c r="J37" t="n">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="K37" t="n">
-        <v>953</v>
+        <v>877</v>
       </c>
       <c r="L37" t="n">
-        <v>935.6</v>
+        <v>892</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1008</v>
+        <v>946</v>
       </c>
       <c r="C38" t="n">
-        <v>878</v>
+        <v>940</v>
       </c>
       <c r="D38" t="n">
-        <v>933</v>
+        <v>1014</v>
       </c>
       <c r="E38" t="n">
-        <v>1048</v>
+        <v>881</v>
       </c>
       <c r="F38" t="n">
-        <v>1066</v>
+        <v>1000</v>
       </c>
       <c r="G38" t="n">
-        <v>1010</v>
+        <v>1094</v>
       </c>
       <c r="H38" t="n">
-        <v>884</v>
+        <v>1024</v>
       </c>
       <c r="I38" t="n">
-        <v>980</v>
+        <v>1006</v>
       </c>
       <c r="J38" t="n">
-        <v>872</v>
+        <v>1091</v>
       </c>
       <c r="K38" t="n">
-        <v>865</v>
+        <v>924</v>
       </c>
       <c r="L38" t="n">
-        <v>954.4</v>
+        <v>992</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>1100</v>
+        <v>962</v>
       </c>
       <c r="C39" t="n">
+        <v>852</v>
+      </c>
+      <c r="D39" t="n">
+        <v>848</v>
+      </c>
+      <c r="E39" t="n">
+        <v>823</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1008</v>
+      </c>
+      <c r="G39" t="n">
+        <v>877</v>
+      </c>
+      <c r="H39" t="n">
+        <v>832</v>
+      </c>
+      <c r="I39" t="n">
+        <v>878</v>
+      </c>
+      <c r="J39" t="n">
+        <v>971</v>
+      </c>
+      <c r="K39" t="n">
         <v>892</v>
       </c>
-      <c r="D39" t="n">
-        <v>776</v>
-      </c>
-      <c r="E39" t="n">
-        <v>965</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1033</v>
-      </c>
-      <c r="G39" t="n">
-        <v>829</v>
-      </c>
-      <c r="H39" t="n">
-        <v>1147</v>
-      </c>
-      <c r="I39" t="n">
-        <v>866</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1003</v>
-      </c>
-      <c r="K39" t="n">
-        <v>997</v>
-      </c>
       <c r="L39" t="n">
-        <v>960.8</v>
+        <v>894.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1102</v>
+        <v>917</v>
       </c>
       <c r="C40" t="n">
-        <v>1002</v>
+        <v>857</v>
       </c>
       <c r="D40" t="n">
-        <v>990</v>
+        <v>935</v>
       </c>
       <c r="E40" t="n">
-        <v>904</v>
+        <v>887</v>
       </c>
       <c r="F40" t="n">
-        <v>1136</v>
+        <v>1036</v>
       </c>
       <c r="G40" t="n">
-        <v>989</v>
+        <v>864</v>
       </c>
       <c r="H40" t="n">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="I40" t="n">
-        <v>1111</v>
+        <v>981</v>
       </c>
       <c r="J40" t="n">
-        <v>937</v>
+        <v>1084</v>
       </c>
       <c r="K40" t="n">
-        <v>1059</v>
+        <v>951</v>
       </c>
       <c r="L40" t="n">
-        <v>1018</v>
+        <v>945.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>967</v>
+        <v>881</v>
       </c>
       <c r="C41" t="n">
-        <v>945</v>
+        <v>821</v>
       </c>
       <c r="D41" t="n">
-        <v>853</v>
+        <v>995</v>
       </c>
       <c r="E41" t="n">
-        <v>856</v>
+        <v>1068</v>
       </c>
       <c r="F41" t="n">
-        <v>1155</v>
+        <v>953</v>
       </c>
       <c r="G41" t="n">
-        <v>1002</v>
+        <v>988</v>
       </c>
       <c r="H41" t="n">
-        <v>1206</v>
+        <v>1025</v>
       </c>
       <c r="I41" t="n">
-        <v>1061</v>
+        <v>946</v>
       </c>
       <c r="J41" t="n">
-        <v>921</v>
+        <v>1064</v>
       </c>
       <c r="K41" t="n">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="L41" t="n">
-        <v>994.7</v>
+        <v>971.2</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>885</v>
+        <v>1004</v>
       </c>
       <c r="C42" t="n">
-        <v>910</v>
+        <v>897</v>
       </c>
       <c r="D42" t="n">
-        <v>835</v>
+        <v>1077</v>
       </c>
       <c r="E42" t="n">
-        <v>977</v>
+        <v>897</v>
       </c>
       <c r="F42" t="n">
-        <v>915</v>
+        <v>801</v>
       </c>
       <c r="G42" t="n">
-        <v>998</v>
+        <v>889</v>
       </c>
       <c r="H42" t="n">
-        <v>995</v>
+        <v>906</v>
       </c>
       <c r="I42" t="n">
-        <v>823</v>
+        <v>939</v>
       </c>
       <c r="J42" t="n">
-        <v>989</v>
+        <v>877</v>
       </c>
       <c r="K42" t="n">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="L42" t="n">
-        <v>916.7</v>
+        <v>914.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>832</v>
+        <v>885</v>
       </c>
       <c r="C43" t="n">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="D43" t="n">
-        <v>1065</v>
+        <v>1099</v>
       </c>
       <c r="E43" t="n">
-        <v>951</v>
+        <v>897</v>
       </c>
       <c r="F43" t="n">
-        <v>1024</v>
+        <v>1096</v>
       </c>
       <c r="G43" t="n">
-        <v>980</v>
+        <v>902</v>
       </c>
       <c r="H43" t="n">
-        <v>1096</v>
+        <v>900</v>
       </c>
       <c r="I43" t="n">
-        <v>926</v>
+        <v>1054</v>
       </c>
       <c r="J43" t="n">
-        <v>1148</v>
+        <v>1056</v>
       </c>
       <c r="K43" t="n">
-        <v>1051</v>
+        <v>1076</v>
       </c>
       <c r="L43" t="n">
-        <v>991.7</v>
+        <v>983.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>1077</v>
+        <v>885</v>
       </c>
       <c r="C44" t="n">
-        <v>980</v>
+        <v>993</v>
       </c>
       <c r="D44" t="n">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E44" t="n">
-        <v>857</v>
+        <v>1054</v>
       </c>
       <c r="F44" t="n">
-        <v>969</v>
+        <v>896</v>
       </c>
       <c r="G44" t="n">
-        <v>884</v>
+        <v>954</v>
       </c>
       <c r="H44" t="n">
-        <v>917</v>
+        <v>865</v>
       </c>
       <c r="I44" t="n">
-        <v>1002</v>
+        <v>950</v>
       </c>
       <c r="J44" t="n">
-        <v>980</v>
+        <v>953</v>
       </c>
       <c r="K44" t="n">
-        <v>901</v>
+        <v>1058</v>
       </c>
       <c r="L44" t="n">
-        <v>940.9</v>
+        <v>944.8</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="C45" t="n">
-        <v>928</v>
+        <v>1131</v>
       </c>
       <c r="D45" t="n">
-        <v>906</v>
+        <v>945</v>
       </c>
       <c r="E45" t="n">
-        <v>859</v>
+        <v>834</v>
       </c>
       <c r="F45" t="n">
-        <v>846</v>
+        <v>916</v>
       </c>
       <c r="G45" t="n">
-        <v>819</v>
+        <v>1002</v>
       </c>
       <c r="H45" t="n">
-        <v>1090</v>
+        <v>862</v>
       </c>
       <c r="I45" t="n">
-        <v>952</v>
+        <v>1153</v>
       </c>
       <c r="J45" t="n">
-        <v>996</v>
+        <v>922</v>
       </c>
       <c r="K45" t="n">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="L45" t="n">
-        <v>947.5</v>
+        <v>984.5</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="C46" t="n">
-        <v>1129</v>
+        <v>919</v>
       </c>
       <c r="D46" t="n">
-        <v>1066</v>
+        <v>1039</v>
       </c>
       <c r="E46" t="n">
-        <v>1115</v>
+        <v>973</v>
       </c>
       <c r="F46" t="n">
-        <v>1117</v>
+        <v>961</v>
       </c>
       <c r="G46" t="n">
-        <v>1045</v>
+        <v>1017</v>
       </c>
       <c r="H46" t="n">
-        <v>803</v>
+        <v>926</v>
       </c>
       <c r="I46" t="n">
-        <v>984</v>
+        <v>953</v>
       </c>
       <c r="J46" t="n">
-        <v>908</v>
+        <v>974</v>
       </c>
       <c r="K46" t="n">
-        <v>929</v>
+        <v>1038</v>
       </c>
       <c r="L46" t="n">
-        <v>999.5</v>
+        <v>970.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>986</v>
+        <v>1081</v>
       </c>
       <c r="C47" t="n">
-        <v>1210</v>
+        <v>907</v>
       </c>
       <c r="D47" t="n">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E47" t="n">
-        <v>1176</v>
+        <v>1068</v>
       </c>
       <c r="F47" t="n">
-        <v>1041</v>
+        <v>1061</v>
       </c>
       <c r="G47" t="n">
-        <v>1107</v>
+        <v>872</v>
       </c>
       <c r="H47" t="n">
-        <v>961</v>
+        <v>1000</v>
       </c>
       <c r="I47" t="n">
+        <v>967</v>
+      </c>
+      <c r="J47" t="n">
         <v>994</v>
       </c>
-      <c r="J47" t="n">
-        <v>1209</v>
-      </c>
       <c r="K47" t="n">
-        <v>995</v>
+        <v>1080</v>
       </c>
       <c r="L47" t="n">
-        <v>1065.1</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>987</v>
+        <v>838</v>
       </c>
       <c r="C48" t="n">
-        <v>1179</v>
+        <v>886</v>
       </c>
       <c r="D48" t="n">
-        <v>1033</v>
+        <v>904</v>
       </c>
       <c r="E48" t="n">
-        <v>886</v>
+        <v>800</v>
       </c>
       <c r="F48" t="n">
-        <v>1022</v>
+        <v>1075</v>
       </c>
       <c r="G48" t="n">
-        <v>964</v>
+        <v>915</v>
       </c>
       <c r="H48" t="n">
-        <v>1153</v>
+        <v>833</v>
       </c>
       <c r="I48" t="n">
-        <v>849</v>
+        <v>1020</v>
       </c>
       <c r="J48" t="n">
-        <v>1059</v>
+        <v>921</v>
       </c>
       <c r="K48" t="n">
-        <v>1069</v>
+        <v>842</v>
       </c>
       <c r="L48" t="n">
-        <v>1020.1</v>
+        <v>903.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1166</v>
+        <v>949</v>
       </c>
       <c r="C49" t="n">
-        <v>1021</v>
+        <v>1147</v>
       </c>
       <c r="D49" t="n">
-        <v>1119</v>
+        <v>969</v>
       </c>
       <c r="E49" t="n">
-        <v>1229</v>
+        <v>957</v>
       </c>
       <c r="F49" t="n">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="G49" t="n">
-        <v>1103</v>
+        <v>907</v>
       </c>
       <c r="H49" t="n">
-        <v>1061</v>
+        <v>981</v>
       </c>
       <c r="I49" t="n">
-        <v>1029</v>
+        <v>882</v>
       </c>
       <c r="J49" t="n">
-        <v>965</v>
+        <v>1125</v>
       </c>
       <c r="K49" t="n">
-        <v>1190</v>
+        <v>1010</v>
       </c>
       <c r="L49" t="n">
-        <v>1086.7</v>
+        <v>989.4</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>1108</v>
+        <v>1020</v>
       </c>
       <c r="C50" t="n">
-        <v>1141</v>
+        <v>863</v>
       </c>
       <c r="D50" t="n">
-        <v>1038</v>
+        <v>983</v>
       </c>
       <c r="E50" t="n">
-        <v>903</v>
+        <v>1012</v>
       </c>
       <c r="F50" t="n">
-        <v>961</v>
+        <v>894</v>
       </c>
       <c r="G50" t="n">
-        <v>1119</v>
+        <v>909</v>
       </c>
       <c r="H50" t="n">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="I50" t="n">
-        <v>969</v>
+        <v>819</v>
       </c>
       <c r="J50" t="n">
-        <v>1142</v>
+        <v>963</v>
       </c>
       <c r="K50" t="n">
-        <v>1029</v>
+        <v>897</v>
       </c>
       <c r="L50" t="n">
-        <v>1041.1</v>
+        <v>935.9</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>845</v>
+        <v>1012</v>
       </c>
       <c r="C51" t="n">
-        <v>1127</v>
+        <v>947</v>
       </c>
       <c r="D51" t="n">
-        <v>1120</v>
+        <v>867</v>
       </c>
       <c r="E51" t="n">
-        <v>1179</v>
+        <v>1056</v>
       </c>
       <c r="F51" t="n">
-        <v>1002</v>
+        <v>846</v>
       </c>
       <c r="G51" t="n">
-        <v>1073</v>
+        <v>962</v>
       </c>
       <c r="H51" t="n">
-        <v>1124</v>
+        <v>986</v>
       </c>
       <c r="I51" t="n">
-        <v>1014</v>
+        <v>884</v>
       </c>
       <c r="J51" t="n">
-        <v>1035</v>
+        <v>977</v>
       </c>
       <c r="K51" t="n">
-        <v>895</v>
+        <v>971</v>
       </c>
       <c r="L51" t="n">
-        <v>1041.4</v>
+        <v>950.8</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1030.22</v>
+        <v>947.2</v>
       </c>
       <c r="C52" t="n">
-        <v>1003.18</v>
+        <v>949.6799999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>988.7</v>
+        <v>953.16</v>
       </c>
       <c r="E52" t="n">
-        <v>999.78</v>
+        <v>951.4</v>
       </c>
       <c r="F52" t="n">
-        <v>1003.68</v>
+        <v>952.86</v>
       </c>
       <c r="G52" t="n">
-        <v>1009</v>
+        <v>951.28</v>
       </c>
       <c r="H52" t="n">
-        <v>1010.88</v>
+        <v>927.86</v>
       </c>
       <c r="I52" t="n">
-        <v>987.48</v>
+        <v>959.3200000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>1007.66</v>
+        <v>953.8</v>
       </c>
       <c r="K52" t="n">
-        <v>1004.08</v>
+        <v>947.48</v>
       </c>
       <c r="L52" t="n">
-        <v>1004.466</v>
+        <v>949.4040000000001</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.94503211975098</v>
+        <v>7.576620817184448</v>
       </c>
       <c r="C2" t="n">
-        <v>7.17434024810791</v>
+        <v>6.863775730133057</v>
       </c>
       <c r="D2" t="n">
-        <v>7.323429346084595</v>
+        <v>7.829063415527344</v>
       </c>
       <c r="E2" t="n">
-        <v>6.431257963180542</v>
+        <v>7.13155722618103</v>
       </c>
       <c r="F2" t="n">
-        <v>6.887371063232422</v>
+        <v>8.829598188400269</v>
       </c>
       <c r="G2" t="n">
-        <v>7.579183340072632</v>
+        <v>8.356252908706665</v>
       </c>
       <c r="H2" t="n">
-        <v>8.452964544296265</v>
+        <v>8.864843130111694</v>
       </c>
       <c r="I2" t="n">
-        <v>6.886468887329102</v>
+        <v>6.6292724609375</v>
       </c>
       <c r="J2" t="n">
-        <v>8.518774271011353</v>
+        <v>7.67248272895813</v>
       </c>
       <c r="K2" t="n">
-        <v>7.347319841384888</v>
+        <v>10.19573378562927</v>
       </c>
       <c r="L2" t="n">
-        <v>7.754614162445068</v>
+        <v>7.994920039176941</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>10.26384043693542</v>
+        <v>9.758903026580811</v>
       </c>
       <c r="C3" t="n">
-        <v>8.25051736831665</v>
+        <v>9.954379796981812</v>
       </c>
       <c r="D3" t="n">
-        <v>9.279345035552979</v>
+        <v>9.601324558258057</v>
       </c>
       <c r="E3" t="n">
-        <v>6.804651498794556</v>
+        <v>8.625357866287231</v>
       </c>
       <c r="F3" t="n">
-        <v>8.818510770797729</v>
+        <v>8.396794080734253</v>
       </c>
       <c r="G3" t="n">
-        <v>8.626981735229492</v>
+        <v>8.419254779815674</v>
       </c>
       <c r="H3" t="n">
-        <v>7.188708543777466</v>
+        <v>7.4307861328125</v>
       </c>
       <c r="I3" t="n">
-        <v>9.554165124893188</v>
+        <v>9.658699035644531</v>
       </c>
       <c r="J3" t="n">
-        <v>6.991229772567749</v>
+        <v>7.516715526580811</v>
       </c>
       <c r="K3" t="n">
-        <v>8.921739339828491</v>
+        <v>7.699853658676147</v>
       </c>
       <c r="L3" t="n">
-        <v>8.469968962669373</v>
+        <v>8.706206846237183</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>7.109384775161743</v>
+        <v>7.746584892272949</v>
       </c>
       <c r="C4" t="n">
-        <v>6.99220085144043</v>
+        <v>7.444602489471436</v>
       </c>
       <c r="D4" t="n">
-        <v>7.74875807762146</v>
+        <v>7.682559251785278</v>
       </c>
       <c r="E4" t="n">
-        <v>7.752717971801758</v>
+        <v>8.387934446334839</v>
       </c>
       <c r="F4" t="n">
-        <v>6.426624059677124</v>
+        <v>7.386543035507202</v>
       </c>
       <c r="G4" t="n">
-        <v>9.218513965606689</v>
+        <v>6.285700798034668</v>
       </c>
       <c r="H4" t="n">
-        <v>9.440454721450806</v>
+        <v>6.400699138641357</v>
       </c>
       <c r="I4" t="n">
-        <v>7.605630874633789</v>
+        <v>6.082456350326538</v>
       </c>
       <c r="J4" t="n">
-        <v>7.373690843582153</v>
+        <v>8.543612957000732</v>
       </c>
       <c r="K4" t="n">
-        <v>8.625014066696167</v>
+        <v>6.483431577682495</v>
       </c>
       <c r="L4" t="n">
-        <v>7.829299020767212</v>
+        <v>7.24441249370575</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>9.985554933547974</v>
+        <v>7.136831760406494</v>
       </c>
       <c r="C5" t="n">
-        <v>8.129791498184204</v>
+        <v>8.00759744644165</v>
       </c>
       <c r="D5" t="n">
-        <v>9.033981323242188</v>
+        <v>7.6766676902771</v>
       </c>
       <c r="E5" t="n">
-        <v>6.989209413528442</v>
+        <v>8.066878795623779</v>
       </c>
       <c r="F5" t="n">
-        <v>8.56766414642334</v>
+        <v>8.697895765304565</v>
       </c>
       <c r="G5" t="n">
-        <v>8.06294584274292</v>
+        <v>6.919622421264648</v>
       </c>
       <c r="H5" t="n">
-        <v>7.618605136871338</v>
+        <v>6.98191237449646</v>
       </c>
       <c r="I5" t="n">
-        <v>6.510942459106445</v>
+        <v>8.788437128067017</v>
       </c>
       <c r="J5" t="n">
-        <v>7.985145568847656</v>
+        <v>6.060482501983643</v>
       </c>
       <c r="K5" t="n">
-        <v>6.44209885597229</v>
+        <v>6.159018516540527</v>
       </c>
       <c r="L5" t="n">
-        <v>7.932593917846679</v>
+        <v>7.449534440040589</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>7.144297361373901</v>
+        <v>7.77371621131897</v>
       </c>
       <c r="C6" t="n">
-        <v>7.308893918991089</v>
+        <v>6.507114171981812</v>
       </c>
       <c r="D6" t="n">
-        <v>7.780181646347046</v>
+        <v>5.579012155532837</v>
       </c>
       <c r="E6" t="n">
-        <v>7.771732807159424</v>
+        <v>5.579447507858276</v>
       </c>
       <c r="F6" t="n">
-        <v>8.985109567642212</v>
+        <v>8.732460021972656</v>
       </c>
       <c r="G6" t="n">
-        <v>7.365719079971313</v>
+        <v>7.891045331954956</v>
       </c>
       <c r="H6" t="n">
-        <v>7.397159576416016</v>
+        <v>5.73366379737854</v>
       </c>
       <c r="I6" t="n">
-        <v>8.488866567611694</v>
+        <v>5.713032960891724</v>
       </c>
       <c r="J6" t="n">
-        <v>5.842122554779053</v>
+        <v>5.72182035446167</v>
       </c>
       <c r="K6" t="n">
-        <v>6.298429250717163</v>
+        <v>7.871073484420776</v>
       </c>
       <c r="L6" t="n">
-        <v>7.438251233100891</v>
+        <v>6.710238599777222</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>10.37755179405212</v>
+        <v>9.12060022354126</v>
       </c>
       <c r="C7" t="n">
-        <v>7.281430244445801</v>
+        <v>9.202878713607788</v>
       </c>
       <c r="D7" t="n">
-        <v>8.567246913909912</v>
+        <v>6.765982151031494</v>
       </c>
       <c r="E7" t="n">
-        <v>7.265481948852539</v>
+        <v>7.396183967590332</v>
       </c>
       <c r="F7" t="n">
-        <v>7.445014953613281</v>
+        <v>7.742730855941772</v>
       </c>
       <c r="G7" t="n">
-        <v>8.938272476196289</v>
+        <v>11.31339073181152</v>
       </c>
       <c r="H7" t="n">
-        <v>7.902934551239014</v>
+        <v>6.745000839233398</v>
       </c>
       <c r="I7" t="n">
-        <v>7.501861333847046</v>
+        <v>7.188650846481323</v>
       </c>
       <c r="J7" t="n">
-        <v>7.791177272796631</v>
+        <v>8.884526491165161</v>
       </c>
       <c r="K7" t="n">
-        <v>9.075357913970947</v>
+        <v>7.301779985427856</v>
       </c>
       <c r="L7" t="n">
-        <v>8.214632940292358</v>
+        <v>8.166172480583191</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>6.905901193618774</v>
+        <v>7.455857038497925</v>
       </c>
       <c r="C8" t="n">
-        <v>9.750637531280518</v>
+        <v>7.191433429718018</v>
       </c>
       <c r="D8" t="n">
-        <v>7.688021898269653</v>
+        <v>7.846259832382202</v>
       </c>
       <c r="E8" t="n">
-        <v>8.974630117416382</v>
+        <v>9.458116292953491</v>
       </c>
       <c r="F8" t="n">
-        <v>7.921294450759888</v>
+        <v>8.897893905639648</v>
       </c>
       <c r="G8" t="n">
-        <v>7.27124547958374</v>
+        <v>8.747326374053955</v>
       </c>
       <c r="H8" t="n">
-        <v>6.511577844619751</v>
+        <v>7.017119407653809</v>
       </c>
       <c r="I8" t="n">
-        <v>8.219607353210449</v>
+        <v>9.391735792160034</v>
       </c>
       <c r="J8" t="n">
-        <v>10.05579805374146</v>
+        <v>8.002201318740845</v>
       </c>
       <c r="K8" t="n">
-        <v>9.131736516952515</v>
+        <v>7.192702054977417</v>
       </c>
       <c r="L8" t="n">
-        <v>8.243045043945312</v>
+        <v>8.120064544677735</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9.373626947402954</v>
+        <v>9.01625394821167</v>
       </c>
       <c r="C9" t="n">
-        <v>10.14280462265015</v>
+        <v>6.866952657699585</v>
       </c>
       <c r="D9" t="n">
-        <v>7.131341218948364</v>
+        <v>7.071017980575562</v>
       </c>
       <c r="E9" t="n">
-        <v>8.077649593353271</v>
+        <v>6.646636724472046</v>
       </c>
       <c r="F9" t="n">
-        <v>7.429075717926025</v>
+        <v>8.110595703125</v>
       </c>
       <c r="G9" t="n">
-        <v>6.96173882484436</v>
+        <v>6.636573791503906</v>
       </c>
       <c r="H9" t="n">
-        <v>7.699974298477173</v>
+        <v>6.601572751998901</v>
       </c>
       <c r="I9" t="n">
-        <v>9.080378770828247</v>
+        <v>7.177841663360596</v>
       </c>
       <c r="J9" t="n">
-        <v>9.75567889213562</v>
+        <v>7.026340246200562</v>
       </c>
       <c r="K9" t="n">
-        <v>9.285853624343872</v>
+        <v>8.099508047103882</v>
       </c>
       <c r="L9" t="n">
-        <v>8.493812251091004</v>
+        <v>7.325329351425171</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.845132827758789</v>
+        <v>7.830268621444702</v>
       </c>
       <c r="C10" t="n">
-        <v>7.124371290206909</v>
+        <v>7.413426876068115</v>
       </c>
       <c r="D10" t="n">
-        <v>7.338290691375732</v>
+        <v>6.656511306762695</v>
       </c>
       <c r="E10" t="n">
-        <v>8.769132614135742</v>
+        <v>8.592862129211426</v>
       </c>
       <c r="F10" t="n">
-        <v>6.322394847869873</v>
+        <v>6.090491056442261</v>
       </c>
       <c r="G10" t="n">
-        <v>6.796696424484253</v>
+        <v>6.376284122467041</v>
       </c>
       <c r="H10" t="n">
-        <v>7.589697599411011</v>
+        <v>6.502089738845825</v>
       </c>
       <c r="I10" t="n">
-        <v>8.713286161422729</v>
+        <v>6.327712297439575</v>
       </c>
       <c r="J10" t="n">
-        <v>6.839562177658081</v>
+        <v>7.459657907485962</v>
       </c>
       <c r="K10" t="n">
-        <v>8.570636510848999</v>
+        <v>8.107221126556396</v>
       </c>
       <c r="L10" t="n">
-        <v>7.390920114517212</v>
+        <v>7.1356525182724</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>8.630992889404297</v>
+        <v>7.928469896316528</v>
       </c>
       <c r="C11" t="n">
-        <v>6.963468790054321</v>
+        <v>7.140581607818604</v>
       </c>
       <c r="D11" t="n">
-        <v>7.228195905685425</v>
+        <v>6.912558078765869</v>
       </c>
       <c r="E11" t="n">
-        <v>6.924496412277222</v>
+        <v>6.339069128036499</v>
       </c>
       <c r="F11" t="n">
-        <v>6.873609781265259</v>
+        <v>6.738015413284302</v>
       </c>
       <c r="G11" t="n">
-        <v>8.861923694610596</v>
+        <v>6.219124794006348</v>
       </c>
       <c r="H11" t="n">
-        <v>6.5809166431427</v>
+        <v>8.079621553421021</v>
       </c>
       <c r="I11" t="n">
-        <v>8.907345533370972</v>
+        <v>6.919910669326782</v>
       </c>
       <c r="J11" t="n">
-        <v>9.772074460983276</v>
+        <v>6.888776063919067</v>
       </c>
       <c r="K11" t="n">
-        <v>7.108983755111694</v>
+        <v>6.656564950942993</v>
       </c>
       <c r="L11" t="n">
-        <v>7.785200786590576</v>
+        <v>6.982269215583801</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>8.14731502532959</v>
+        <v>10.50777006149292</v>
       </c>
       <c r="C12" t="n">
-        <v>8.101441860198975</v>
+        <v>10.25428295135498</v>
       </c>
       <c r="D12" t="n">
-        <v>10.13162660598755</v>
+        <v>8.876413822174072</v>
       </c>
       <c r="E12" t="n">
-        <v>9.886795520782471</v>
+        <v>8.100338220596313</v>
       </c>
       <c r="F12" t="n">
-        <v>9.343218564987183</v>
+        <v>7.288379669189453</v>
       </c>
       <c r="G12" t="n">
-        <v>9.387345790863037</v>
+        <v>8.089802026748657</v>
       </c>
       <c r="H12" t="n">
-        <v>10.59642624855042</v>
+        <v>8.076201915740967</v>
       </c>
       <c r="I12" t="n">
-        <v>7.679519414901733</v>
+        <v>8.362636804580688</v>
       </c>
       <c r="J12" t="n">
-        <v>7.809666156768799</v>
+        <v>8.588785886764526</v>
       </c>
       <c r="K12" t="n">
-        <v>8.309354782104492</v>
+        <v>7.746198654174805</v>
       </c>
       <c r="L12" t="n">
-        <v>8.939270997047425</v>
+        <v>8.589081001281738</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>6.200889587402344</v>
+        <v>6.149389028549194</v>
       </c>
       <c r="C13" t="n">
-        <v>6.530585289001465</v>
+        <v>9.308109045028687</v>
       </c>
       <c r="D13" t="n">
-        <v>6.649218320846558</v>
+        <v>7.150876760482788</v>
       </c>
       <c r="E13" t="n">
-        <v>8.862046480178833</v>
+        <v>7.860979080200195</v>
       </c>
       <c r="F13" t="n">
-        <v>8.265941143035889</v>
+        <v>7.058079719543457</v>
       </c>
       <c r="G13" t="n">
-        <v>6.990232944488525</v>
+        <v>6.518892526626587</v>
       </c>
       <c r="H13" t="n">
-        <v>6.762794971466064</v>
+        <v>6.390039682388306</v>
       </c>
       <c r="I13" t="n">
-        <v>6.485506534576416</v>
+        <v>6.568774223327637</v>
       </c>
       <c r="J13" t="n">
-        <v>7.777219533920288</v>
+        <v>6.041694402694702</v>
       </c>
       <c r="K13" t="n">
-        <v>7.242566347122192</v>
+        <v>6.849061489105225</v>
       </c>
       <c r="L13" t="n">
-        <v>7.176700115203857</v>
+        <v>6.989589595794678</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.021110773086548</v>
+        <v>7.888783693313599</v>
       </c>
       <c r="C14" t="n">
-        <v>7.726797342300415</v>
+        <v>7.244426488876343</v>
       </c>
       <c r="D14" t="n">
-        <v>8.505337953567505</v>
+        <v>8.199691534042358</v>
       </c>
       <c r="E14" t="n">
-        <v>10.1840660572052</v>
+        <v>7.319653034210205</v>
       </c>
       <c r="F14" t="n">
-        <v>8.005601406097412</v>
+        <v>7.132918119430542</v>
       </c>
       <c r="G14" t="n">
-        <v>7.101403713226318</v>
+        <v>7.363960027694702</v>
       </c>
       <c r="H14" t="n">
-        <v>6.75128436088562</v>
+        <v>7.101165294647217</v>
       </c>
       <c r="I14" t="n">
-        <v>10.23698759078979</v>
+        <v>7.084434986114502</v>
       </c>
       <c r="J14" t="n">
-        <v>10.56584596633911</v>
+        <v>8.294628620147705</v>
       </c>
       <c r="K14" t="n">
-        <v>7.962729930877686</v>
+        <v>10.90454292297363</v>
       </c>
       <c r="L14" t="n">
-        <v>8.406116509437561</v>
+        <v>7.85342047214508</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>8.680872201919556</v>
+        <v>8.52649974822998</v>
       </c>
       <c r="C15" t="n">
-        <v>7.757236957550049</v>
+        <v>6.414193630218506</v>
       </c>
       <c r="D15" t="n">
-        <v>8.040520429611206</v>
+        <v>6.918977499008179</v>
       </c>
       <c r="E15" t="n">
-        <v>7.534306764602661</v>
+        <v>8.193070411682129</v>
       </c>
       <c r="F15" t="n">
-        <v>8.401614665985107</v>
+        <v>6.459969043731689</v>
       </c>
       <c r="G15" t="n">
-        <v>8.061977386474609</v>
+        <v>7.248942613601685</v>
       </c>
       <c r="H15" t="n">
-        <v>7.073964834213257</v>
+        <v>9.312639236450195</v>
       </c>
       <c r="I15" t="n">
-        <v>6.888953685760498</v>
+        <v>8.127119302749634</v>
       </c>
       <c r="J15" t="n">
-        <v>7.472941398620605</v>
+        <v>8.005590677261353</v>
       </c>
       <c r="K15" t="n">
-        <v>6.519896268844604</v>
+        <v>7.500186920166016</v>
       </c>
       <c r="L15" t="n">
-        <v>7.643228459358215</v>
+        <v>7.670718908309937</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>9.245445489883423</v>
+        <v>8.273273229598999</v>
       </c>
       <c r="C16" t="n">
-        <v>7.81807804107666</v>
+        <v>10.14786243438721</v>
       </c>
       <c r="D16" t="n">
-        <v>7.127336502075195</v>
+        <v>6.571865081787109</v>
       </c>
       <c r="E16" t="n">
-        <v>6.929839611053467</v>
+        <v>9.857706546783447</v>
       </c>
       <c r="F16" t="n">
-        <v>7.229580163955688</v>
+        <v>7.54369592666626</v>
       </c>
       <c r="G16" t="n">
-        <v>7.380311012268066</v>
+        <v>7.040174245834351</v>
       </c>
       <c r="H16" t="n">
-        <v>9.25542163848877</v>
+        <v>9.439997673034668</v>
       </c>
       <c r="I16" t="n">
-        <v>7.295522451400757</v>
+        <v>6.940072298049927</v>
       </c>
       <c r="J16" t="n">
-        <v>7.210231781005859</v>
+        <v>7.289506673812866</v>
       </c>
       <c r="K16" t="n">
-        <v>8.707860469818115</v>
+        <v>9.644250154495239</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8199627161026</v>
+        <v>8.274840426445007</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>8.521317481994629</v>
+        <v>6.888577699661255</v>
       </c>
       <c r="C17" t="n">
-        <v>10.49719667434692</v>
+        <v>8.213036775588989</v>
       </c>
       <c r="D17" t="n">
-        <v>9.615024566650391</v>
+        <v>8.489297866821289</v>
       </c>
       <c r="E17" t="n">
-        <v>7.345383167266846</v>
+        <v>10.49538087844849</v>
       </c>
       <c r="F17" t="n">
-        <v>6.933462619781494</v>
+        <v>9.077388525009155</v>
       </c>
       <c r="G17" t="n">
-        <v>9.053433179855347</v>
+        <v>8.81343150138855</v>
       </c>
       <c r="H17" t="n">
-        <v>7.598245143890381</v>
+        <v>8.681501388549805</v>
       </c>
       <c r="I17" t="n">
-        <v>8.193694829940796</v>
+        <v>7.789169073104858</v>
       </c>
       <c r="J17" t="n">
-        <v>9.764082908630371</v>
+        <v>7.158844470977783</v>
       </c>
       <c r="K17" t="n">
-        <v>9.247463464736938</v>
+        <v>7.14190149307251</v>
       </c>
       <c r="L17" t="n">
-        <v>8.676930403709411</v>
+        <v>8.274852967262268</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>8.676965951919556</v>
+        <v>8.436476469039917</v>
       </c>
       <c r="C18" t="n">
-        <v>6.894046306610107</v>
+        <v>7.818540811538696</v>
       </c>
       <c r="D18" t="n">
-        <v>7.230201482772827</v>
+        <v>7.463856935501099</v>
       </c>
       <c r="E18" t="n">
-        <v>7.630682706832886</v>
+        <v>8.772255897521973</v>
       </c>
       <c r="F18" t="n">
-        <v>8.056024074554443</v>
+        <v>7.244626998901367</v>
       </c>
       <c r="G18" t="n">
-        <v>8.714819669723511</v>
+        <v>6.951006889343262</v>
       </c>
       <c r="H18" t="n">
-        <v>8.022115468978882</v>
+        <v>8.02827787399292</v>
       </c>
       <c r="I18" t="n">
-        <v>7.343426942825317</v>
+        <v>8.870279550552368</v>
       </c>
       <c r="J18" t="n">
-        <v>7.604259490966797</v>
+        <v>7.407508611679077</v>
       </c>
       <c r="K18" t="n">
-        <v>7.256106376647949</v>
+        <v>8.396546125411987</v>
       </c>
       <c r="L18" t="n">
-        <v>7.742864847183228</v>
+        <v>7.938937616348267</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>7.987966299057007</v>
+        <v>7.223682403564453</v>
       </c>
       <c r="C19" t="n">
-        <v>6.919862985610962</v>
+        <v>7.950737714767456</v>
       </c>
       <c r="D19" t="n">
-        <v>6.587236642837524</v>
+        <v>10.0291805267334</v>
       </c>
       <c r="E19" t="n">
-        <v>8.638978004455566</v>
+        <v>8.025537729263306</v>
       </c>
       <c r="F19" t="n">
-        <v>7.750260829925537</v>
+        <v>8.788497686386108</v>
       </c>
       <c r="G19" t="n">
-        <v>7.2884202003479</v>
+        <v>8.813431024551392</v>
       </c>
       <c r="H19" t="n">
-        <v>6.23860764503479</v>
+        <v>6.335058927536011</v>
       </c>
       <c r="I19" t="n">
-        <v>7.047030210494995</v>
+        <v>6.304608106613159</v>
       </c>
       <c r="J19" t="n">
-        <v>8.794592618942261</v>
+        <v>9.68518853187561</v>
       </c>
       <c r="K19" t="n">
-        <v>6.544820785522461</v>
+        <v>8.154621601104736</v>
       </c>
       <c r="L19" t="n">
-        <v>7.379777622222901</v>
+        <v>8.131054425239563</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>7.34785532951355</v>
+        <v>8.042491674423218</v>
       </c>
       <c r="C20" t="n">
-        <v>10.69130158424377</v>
+        <v>9.131580114364624</v>
       </c>
       <c r="D20" t="n">
-        <v>8.288372039794922</v>
+        <v>9.657531261444092</v>
       </c>
       <c r="E20" t="n">
-        <v>9.75667405128479</v>
+        <v>10.72132873535156</v>
       </c>
       <c r="F20" t="n">
-        <v>9.644458770751953</v>
+        <v>12.40179538726807</v>
       </c>
       <c r="G20" t="n">
-        <v>7.169744491577148</v>
+        <v>11.27944922447205</v>
       </c>
       <c r="H20" t="n">
-        <v>10.77103924751282</v>
+        <v>7.791231870651245</v>
       </c>
       <c r="I20" t="n">
-        <v>7.378233432769775</v>
+        <v>9.132947444915771</v>
       </c>
       <c r="J20" t="n">
-        <v>8.450461626052856</v>
+        <v>10.61466574668884</v>
       </c>
       <c r="K20" t="n">
-        <v>10.92268705368042</v>
+        <v>6.651251554489136</v>
       </c>
       <c r="L20" t="n">
-        <v>9.0420827627182</v>
+        <v>9.54242730140686</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>6.878989219665527</v>
+        <v>6.819459438323975</v>
       </c>
       <c r="C21" t="n">
-        <v>7.365731954574585</v>
+        <v>8.745695114135742</v>
       </c>
       <c r="D21" t="n">
-        <v>8.343745708465576</v>
+        <v>6.854525089263916</v>
       </c>
       <c r="E21" t="n">
-        <v>7.596137046813965</v>
+        <v>9.182265758514404</v>
       </c>
       <c r="F21" t="n">
-        <v>9.854406118392944</v>
+        <v>10.29415202140808</v>
       </c>
       <c r="G21" t="n">
-        <v>7.043060779571533</v>
+        <v>7.892587661743164</v>
       </c>
       <c r="H21" t="n">
-        <v>7.553244113922119</v>
+        <v>8.751729726791382</v>
       </c>
       <c r="I21" t="n">
-        <v>7.074521541595459</v>
+        <v>8.813667058944702</v>
       </c>
       <c r="J21" t="n">
-        <v>6.758374214172363</v>
+        <v>7.701384544372559</v>
       </c>
       <c r="K21" t="n">
-        <v>7.089457988739014</v>
+        <v>7.638354778289795</v>
       </c>
       <c r="L21" t="n">
-        <v>7.555766868591308</v>
+        <v>8.269382119178772</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.304455995559692</v>
+        <v>5.960415124893188</v>
       </c>
       <c r="C22" t="n">
-        <v>5.509464502334595</v>
+        <v>7.631996154785156</v>
       </c>
       <c r="D22" t="n">
-        <v>6.509897232055664</v>
+        <v>6.609532356262207</v>
       </c>
       <c r="E22" t="n">
-        <v>7.592671394348145</v>
+        <v>6.292532444000244</v>
       </c>
       <c r="F22" t="n">
-        <v>5.870035409927368</v>
+        <v>8.08637547492981</v>
       </c>
       <c r="G22" t="n">
-        <v>6.177266359329224</v>
+        <v>9.425627708435059</v>
       </c>
       <c r="H22" t="n">
-        <v>8.21507716178894</v>
+        <v>6.892568349838257</v>
       </c>
       <c r="I22" t="n">
-        <v>9.01004695892334</v>
+        <v>6.80579948425293</v>
       </c>
       <c r="J22" t="n">
-        <v>6.421619892120361</v>
+        <v>6.989309310913086</v>
       </c>
       <c r="K22" t="n">
-        <v>5.801235198974609</v>
+        <v>6.53652024269104</v>
       </c>
       <c r="L22" t="n">
-        <v>6.741177010536194</v>
+        <v>7.123067665100097</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>9.006054401397705</v>
+        <v>9.343014478683472</v>
       </c>
       <c r="C23" t="n">
-        <v>8.53772759437561</v>
+        <v>8.752593994140625</v>
       </c>
       <c r="D23" t="n">
-        <v>8.955666542053223</v>
+        <v>8.1372389793396</v>
       </c>
       <c r="E23" t="n">
-        <v>9.242999315261841</v>
+        <v>9.087352275848389</v>
       </c>
       <c r="F23" t="n">
-        <v>9.275342464447021</v>
+        <v>8.525202751159668</v>
       </c>
       <c r="G23" t="n">
-        <v>7.367269039154053</v>
+        <v>11.16813349723816</v>
       </c>
       <c r="H23" t="n">
-        <v>7.730807304382324</v>
+        <v>8.706715822219849</v>
       </c>
       <c r="I23" t="n">
-        <v>8.785136938095093</v>
+        <v>8.240483283996582</v>
       </c>
       <c r="J23" t="n">
-        <v>10.92568731307983</v>
+        <v>9.490576982498169</v>
       </c>
       <c r="K23" t="n">
-        <v>9.309769868850708</v>
+        <v>8.08283805847168</v>
       </c>
       <c r="L23" t="n">
-        <v>8.913646078109741</v>
+        <v>8.953415012359619</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>8.435033798217773</v>
+        <v>9.765178442001343</v>
       </c>
       <c r="C24" t="n">
-        <v>7.747341394424438</v>
+        <v>7.993820190429688</v>
       </c>
       <c r="D24" t="n">
-        <v>9.800018310546875</v>
+        <v>11.81839632987976</v>
       </c>
       <c r="E24" t="n">
-        <v>7.586173534393311</v>
+        <v>8.757502555847168</v>
       </c>
       <c r="F24" t="n">
-        <v>9.001131772994995</v>
+        <v>12.75231313705444</v>
       </c>
       <c r="G24" t="n">
-        <v>8.313339710235596</v>
+        <v>9.303165435791016</v>
       </c>
       <c r="H24" t="n">
-        <v>11.30573749542236</v>
+        <v>10.85685729980469</v>
       </c>
       <c r="I24" t="n">
-        <v>7.908331394195557</v>
+        <v>10.34660029411316</v>
       </c>
       <c r="J24" t="n">
-        <v>8.48039174079895</v>
+        <v>10.33031916618347</v>
       </c>
       <c r="K24" t="n">
-        <v>9.08735990524292</v>
+        <v>8.079577922821045</v>
       </c>
       <c r="L24" t="n">
-        <v>8.766485905647277</v>
+        <v>10.00037307739258</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>7.705893039703369</v>
+        <v>7.883840560913086</v>
       </c>
       <c r="C25" t="n">
-        <v>7.258039236068726</v>
+        <v>6.522225856781006</v>
       </c>
       <c r="D25" t="n">
-        <v>7.576194047927856</v>
+        <v>7.351187467575073</v>
       </c>
       <c r="E25" t="n">
-        <v>7.163772821426392</v>
+        <v>7.39010214805603</v>
       </c>
       <c r="F25" t="n">
-        <v>7.436139106750488</v>
+        <v>8.79677939414978</v>
       </c>
       <c r="G25" t="n">
-        <v>8.474539518356323</v>
+        <v>7.556258201599121</v>
       </c>
       <c r="H25" t="n">
-        <v>6.946320056915283</v>
+        <v>7.81928563117981</v>
       </c>
       <c r="I25" t="n">
-        <v>7.226602792739868</v>
+        <v>10.52905869483948</v>
       </c>
       <c r="J25" t="n">
-        <v>7.469959735870361</v>
+        <v>12.37690186500549</v>
       </c>
       <c r="K25" t="n">
-        <v>6.870989322662354</v>
+        <v>8.636903524398804</v>
       </c>
       <c r="L25" t="n">
-        <v>7.412844967842102</v>
+        <v>8.486254334449768</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>9.654399394989014</v>
+        <v>11.98999643325806</v>
       </c>
       <c r="C26" t="n">
-        <v>8.494889497756958</v>
+        <v>8.079393863677979</v>
       </c>
       <c r="D26" t="n">
-        <v>6.587238788604736</v>
+        <v>6.741969585418701</v>
       </c>
       <c r="E26" t="n">
-        <v>8.837496280670166</v>
+        <v>8.430455207824707</v>
       </c>
       <c r="F26" t="n">
-        <v>6.56779146194458</v>
+        <v>6.308130264282227</v>
       </c>
       <c r="G26" t="n">
-        <v>8.132776737213135</v>
+        <v>8.801464080810547</v>
       </c>
       <c r="H26" t="n">
-        <v>6.611174821853638</v>
+        <v>7.489749193191528</v>
       </c>
       <c r="I26" t="n">
-        <v>7.431052923202515</v>
+        <v>7.105997323989868</v>
       </c>
       <c r="J26" t="n">
-        <v>7.500389814376831</v>
+        <v>6.170110464096069</v>
       </c>
       <c r="K26" t="n">
-        <v>9.977072238922119</v>
+        <v>8.464364767074585</v>
       </c>
       <c r="L26" t="n">
-        <v>7.979428195953369</v>
+        <v>7.958163118362426</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>9.581590175628662</v>
+        <v>6.791613817214966</v>
       </c>
       <c r="C27" t="n">
-        <v>10.62293982505798</v>
+        <v>8.373116254806519</v>
       </c>
       <c r="D27" t="n">
-        <v>9.211513042449951</v>
+        <v>10.07171750068665</v>
       </c>
       <c r="E27" t="n">
-        <v>8.202136278152466</v>
+        <v>8.362650394439697</v>
       </c>
       <c r="F27" t="n">
-        <v>7.577199935913086</v>
+        <v>7.886893272399902</v>
       </c>
       <c r="G27" t="n">
-        <v>9.996537446975708</v>
+        <v>8.505780935287476</v>
       </c>
       <c r="H27" t="n">
-        <v>9.458925485610962</v>
+        <v>9.574395656585693</v>
       </c>
       <c r="I27" t="n">
-        <v>11.78101181983948</v>
+        <v>11.38655018806458</v>
       </c>
       <c r="J27" t="n">
-        <v>7.191688537597656</v>
+        <v>6.936671495437622</v>
       </c>
       <c r="K27" t="n">
-        <v>6.898445844650269</v>
+        <v>7.274548530578613</v>
       </c>
       <c r="L27" t="n">
-        <v>9.052198839187621</v>
+        <v>8.516393804550171</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>10.45289540290833</v>
+        <v>7.620021104812622</v>
       </c>
       <c r="C28" t="n">
-        <v>8.233853816986084</v>
+        <v>7.678548336029053</v>
       </c>
       <c r="D28" t="n">
-        <v>8.948230028152466</v>
+        <v>8.336395978927612</v>
       </c>
       <c r="E28" t="n">
-        <v>9.471912860870361</v>
+        <v>9.800790786743164</v>
       </c>
       <c r="F28" t="n">
-        <v>8.549278020858765</v>
+        <v>8.930762052536011</v>
       </c>
       <c r="G28" t="n">
-        <v>7.345382452011108</v>
+        <v>9.119102239608765</v>
       </c>
       <c r="H28" t="n">
-        <v>7.270585775375366</v>
+        <v>10.71634197235107</v>
       </c>
       <c r="I28" t="n">
-        <v>9.41054368019104</v>
+        <v>8.961784362792969</v>
       </c>
       <c r="J28" t="n">
-        <v>9.082356452941895</v>
+        <v>8.416905403137207</v>
       </c>
       <c r="K28" t="n">
-        <v>9.003583908081055</v>
+        <v>10.06508326530457</v>
       </c>
       <c r="L28" t="n">
-        <v>8.776862239837646</v>
+        <v>8.964573550224305</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>9.629985809326172</v>
+        <v>7.284520149230957</v>
       </c>
       <c r="C29" t="n">
-        <v>8.705862522125244</v>
+        <v>7.450573444366455</v>
       </c>
       <c r="D29" t="n">
-        <v>6.838722467422485</v>
+        <v>11.02252221107483</v>
       </c>
       <c r="E29" t="n">
-        <v>8.277422189712524</v>
+        <v>8.287836074829102</v>
       </c>
       <c r="F29" t="n">
-        <v>9.50778341293335</v>
+        <v>8.994946241378784</v>
       </c>
       <c r="G29" t="n">
-        <v>9.033526659011841</v>
+        <v>9.672002077102661</v>
       </c>
       <c r="H29" t="n">
-        <v>9.756102323532104</v>
+        <v>7.240636110305786</v>
       </c>
       <c r="I29" t="n">
-        <v>7.017778635025024</v>
+        <v>6.652205467224121</v>
       </c>
       <c r="J29" t="n">
-        <v>9.440416097640991</v>
+        <v>7.236647129058838</v>
       </c>
       <c r="K29" t="n">
-        <v>7.185800313949585</v>
+        <v>9.149986982345581</v>
       </c>
       <c r="L29" t="n">
-        <v>8.539340043067932</v>
+        <v>8.299187588691712</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>10.32162404060364</v>
+        <v>9.676292896270752</v>
       </c>
       <c r="C30" t="n">
-        <v>9.204553127288818</v>
+        <v>7.320074081420898</v>
       </c>
       <c r="D30" t="n">
-        <v>8.293006181716919</v>
+        <v>9.372934818267822</v>
       </c>
       <c r="E30" t="n">
-        <v>8.658954620361328</v>
+        <v>9.179052829742432</v>
       </c>
       <c r="F30" t="n">
-        <v>9.191595792770386</v>
+        <v>7.421371459960938</v>
       </c>
       <c r="G30" t="n">
-        <v>8.637533187866211</v>
+        <v>9.742706775665283</v>
       </c>
       <c r="H30" t="n">
-        <v>8.523334503173828</v>
+        <v>8.17869758605957</v>
       </c>
       <c r="I30" t="n">
-        <v>7.532423496246338</v>
+        <v>9.917633771896362</v>
       </c>
       <c r="J30" t="n">
-        <v>7.243152379989624</v>
+        <v>7.753533363342285</v>
       </c>
       <c r="K30" t="n">
-        <v>7.388761043548584</v>
+        <v>10.12342834472656</v>
       </c>
       <c r="L30" t="n">
-        <v>8.499493837356567</v>
+        <v>8.868572592735291</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.136362552642822</v>
+        <v>8.80807900428772</v>
       </c>
       <c r="C31" t="n">
-        <v>6.181909084320068</v>
+        <v>7.581724882125854</v>
       </c>
       <c r="D31" t="n">
-        <v>7.523198843002319</v>
+        <v>8.356652498245239</v>
       </c>
       <c r="E31" t="n">
-        <v>7.473942995071411</v>
+        <v>9.635233163833618</v>
       </c>
       <c r="F31" t="n">
-        <v>10.0738365650177</v>
+        <v>8.174139738082886</v>
       </c>
       <c r="G31" t="n">
-        <v>7.318910598754883</v>
+        <v>7.897064208984375</v>
       </c>
       <c r="H31" t="n">
-        <v>9.86285400390625</v>
+        <v>7.796151876449585</v>
       </c>
       <c r="I31" t="n">
-        <v>8.210083246231079</v>
+        <v>7.610646963119507</v>
       </c>
       <c r="J31" t="n">
-        <v>8.516783475875854</v>
+        <v>7.415170431137085</v>
       </c>
       <c r="K31" t="n">
-        <v>6.991204738616943</v>
+        <v>7.125943422317505</v>
       </c>
       <c r="L31" t="n">
-        <v>8.028908610343933</v>
+        <v>8.040080618858337</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>7.75076961517334</v>
+        <v>7.091036558151245</v>
       </c>
       <c r="C32" t="n">
-        <v>10.07631230354309</v>
+        <v>9.564457893371582</v>
       </c>
       <c r="D32" t="n">
-        <v>10.26739192008972</v>
+        <v>7.148461580276489</v>
       </c>
       <c r="E32" t="n">
-        <v>6.830631732940674</v>
+        <v>7.375908613204956</v>
       </c>
       <c r="F32" t="n">
-        <v>6.983391046524048</v>
+        <v>8.293822526931763</v>
       </c>
       <c r="G32" t="n">
-        <v>8.676427841186523</v>
+        <v>9.4537193775177</v>
       </c>
       <c r="H32" t="n">
-        <v>9.230993986129761</v>
+        <v>7.774210453033447</v>
       </c>
       <c r="I32" t="n">
-        <v>9.118756055831909</v>
+        <v>9.786828517913818</v>
       </c>
       <c r="J32" t="n">
-        <v>6.698063135147095</v>
+        <v>7.321442604064941</v>
       </c>
       <c r="K32" t="n">
-        <v>8.835011959075928</v>
+        <v>8.677793741226196</v>
       </c>
       <c r="L32" t="n">
-        <v>8.446774959564209</v>
+        <v>8.248768186569214</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>7.026740074157715</v>
+        <v>9.08286190032959</v>
       </c>
       <c r="C33" t="n">
-        <v>7.807660341262817</v>
+        <v>9.05977201461792</v>
       </c>
       <c r="D33" t="n">
-        <v>12.67348170280457</v>
+        <v>9.121689796447754</v>
       </c>
       <c r="E33" t="n">
-        <v>7.485045194625854</v>
+        <v>8.851103067398071</v>
       </c>
       <c r="F33" t="n">
-        <v>9.869363307952881</v>
+        <v>10.13600039482117</v>
       </c>
       <c r="G33" t="n">
-        <v>8.516408443450928</v>
+        <v>8.81145453453064</v>
       </c>
       <c r="H33" t="n">
-        <v>9.693295478820801</v>
+        <v>7.978663206100464</v>
       </c>
       <c r="I33" t="n">
-        <v>7.801714181900024</v>
+        <v>8.506253004074097</v>
       </c>
       <c r="J33" t="n">
-        <v>8.650168418884277</v>
+        <v>11.72364377975464</v>
       </c>
       <c r="K33" t="n">
-        <v>9.103799104690552</v>
+        <v>10.22565388679504</v>
       </c>
       <c r="L33" t="n">
-        <v>8.862767624855042</v>
+        <v>9.349709558486939</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>8.179783821105957</v>
+        <v>6.915472507476807</v>
       </c>
       <c r="C34" t="n">
-        <v>6.488594532012939</v>
+        <v>7.340370893478394</v>
       </c>
       <c r="D34" t="n">
-        <v>7.341395616531372</v>
+        <v>8.384397745132446</v>
       </c>
       <c r="E34" t="n">
-        <v>8.790130376815796</v>
+        <v>7.98065710067749</v>
       </c>
       <c r="F34" t="n">
-        <v>6.514553070068359</v>
+        <v>9.332044363021851</v>
       </c>
       <c r="G34" t="n">
-        <v>8.171274662017822</v>
+        <v>9.272204637527466</v>
       </c>
       <c r="H34" t="n">
-        <v>6.269196271896362</v>
+        <v>8.488300323486328</v>
       </c>
       <c r="I34" t="n">
-        <v>7.589736223220825</v>
+        <v>7.90885066986084</v>
       </c>
       <c r="J34" t="n">
-        <v>6.678153514862061</v>
+        <v>7.29050350189209</v>
       </c>
       <c r="K34" t="n">
-        <v>8.250548124313354</v>
+        <v>9.619098901748657</v>
       </c>
       <c r="L34" t="n">
-        <v>7.427336621284485</v>
+        <v>8.253190064430237</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>8.24951696395874</v>
+        <v>8.570082664489746</v>
       </c>
       <c r="C35" t="n">
-        <v>7.549888372421265</v>
+        <v>12.25921559333801</v>
       </c>
       <c r="D35" t="n">
-        <v>9.444414615631104</v>
+        <v>8.533180475234985</v>
       </c>
       <c r="E35" t="n">
-        <v>7.181293487548828</v>
+        <v>9.489623069763184</v>
       </c>
       <c r="F35" t="n">
-        <v>7.109012365341187</v>
+        <v>10.46770453453064</v>
       </c>
       <c r="G35" t="n">
-        <v>9.285379648208618</v>
+        <v>8.323725700378418</v>
       </c>
       <c r="H35" t="n">
-        <v>7.537877082824707</v>
+        <v>9.752919435501099</v>
       </c>
       <c r="I35" t="n">
-        <v>7.249128341674805</v>
+        <v>9.829712867736816</v>
       </c>
       <c r="J35" t="n">
-        <v>8.607616186141968</v>
+        <v>9.048315286636353</v>
       </c>
       <c r="K35" t="n">
-        <v>9.738168716430664</v>
+        <v>9.988288879394531</v>
       </c>
       <c r="L35" t="n">
-        <v>8.195229578018189</v>
+        <v>9.626276850700378</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>10.05931425094604</v>
+        <v>10.63256478309631</v>
       </c>
       <c r="C36" t="n">
-        <v>9.785027503967285</v>
+        <v>10.003249168396</v>
       </c>
       <c r="D36" t="n">
-        <v>10.86025905609131</v>
+        <v>10.28250336647034</v>
       </c>
       <c r="E36" t="n">
-        <v>9.321251392364502</v>
+        <v>10.49099063873291</v>
       </c>
       <c r="F36" t="n">
-        <v>10.17972779273987</v>
+        <v>10.88289618492126</v>
       </c>
       <c r="G36" t="n">
-        <v>9.421000003814697</v>
+        <v>10.3503212928772</v>
       </c>
       <c r="H36" t="n">
-        <v>9.391106605529785</v>
+        <v>9.500643014907837</v>
       </c>
       <c r="I36" t="n">
-        <v>11.8251006603241</v>
+        <v>10.27252960205078</v>
       </c>
       <c r="J36" t="n">
-        <v>8.967182874679565</v>
+        <v>11.4673330783844</v>
       </c>
       <c r="K36" t="n">
-        <v>8.304922103881836</v>
+        <v>9.299132347106934</v>
       </c>
       <c r="L36" t="n">
-        <v>9.811489224433899</v>
+        <v>10.3182163476944</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>7.548889398574829</v>
+        <v>6.776876926422119</v>
       </c>
       <c r="C37" t="n">
-        <v>6.797199249267578</v>
+        <v>7.19974684715271</v>
       </c>
       <c r="D37" t="n">
-        <v>6.480022430419922</v>
+        <v>7.52587366104126</v>
       </c>
       <c r="E37" t="n">
-        <v>8.639996528625488</v>
+        <v>6.663181304931641</v>
       </c>
       <c r="F37" t="n">
-        <v>7.755226373672485</v>
+        <v>8.062439680099487</v>
       </c>
       <c r="G37" t="n">
-        <v>6.530868053436279</v>
+        <v>7.039175510406494</v>
       </c>
       <c r="H37" t="n">
-        <v>7.273462295532227</v>
+        <v>6.95269250869751</v>
       </c>
       <c r="I37" t="n">
-        <v>6.316413164138794</v>
+        <v>7.233654975891113</v>
       </c>
       <c r="J37" t="n">
-        <v>6.27250337600708</v>
+        <v>7.056731462478638</v>
       </c>
       <c r="K37" t="n">
-        <v>7.058038711547852</v>
+        <v>7.183788537979126</v>
       </c>
       <c r="L37" t="n">
-        <v>7.067261958122254</v>
+        <v>7.16941614151001</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>8.534729957580566</v>
+        <v>7.991627931594849</v>
       </c>
       <c r="C38" t="n">
-        <v>6.597207546234131</v>
+        <v>7.322477340698242</v>
       </c>
       <c r="D38" t="n">
-        <v>7.420087575912476</v>
+        <v>10.50283360481262</v>
       </c>
       <c r="E38" t="n">
-        <v>8.403167724609375</v>
+        <v>8.173143148422241</v>
       </c>
       <c r="F38" t="n">
-        <v>9.793119668960571</v>
+        <v>8.196081638336182</v>
       </c>
       <c r="G38" t="n">
-        <v>7.078084945678711</v>
+        <v>10.01122760772705</v>
       </c>
       <c r="H38" t="n">
-        <v>6.906916856765747</v>
+        <v>9.024993181228638</v>
       </c>
       <c r="I38" t="n">
-        <v>7.985181093215942</v>
+        <v>7.539836883544922</v>
       </c>
       <c r="J38" t="n">
-        <v>7.068507194519043</v>
+        <v>8.954054832458496</v>
       </c>
       <c r="K38" t="n">
-        <v>6.700414180755615</v>
+        <v>7.043164968490601</v>
       </c>
       <c r="L38" t="n">
-        <v>7.648741674423218</v>
+        <v>8.475944113731384</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>9.493330240249634</v>
+        <v>7.38325572013855</v>
       </c>
       <c r="C39" t="n">
-        <v>6.777219533920288</v>
+        <v>6.269368648529053</v>
       </c>
       <c r="D39" t="n">
-        <v>6.713418483734131</v>
+        <v>6.506239175796509</v>
       </c>
       <c r="E39" t="n">
-        <v>9.580615043640137</v>
+        <v>7.166834115982056</v>
       </c>
       <c r="F39" t="n">
-        <v>7.068981170654297</v>
+        <v>9.394248247146606</v>
       </c>
       <c r="G39" t="n">
-        <v>6.641146898269653</v>
+        <v>6.673153877258301</v>
       </c>
       <c r="H39" t="n">
-        <v>8.831549644470215</v>
+        <v>7.641201257705688</v>
       </c>
       <c r="I39" t="n">
-        <v>6.47847318649292</v>
+        <v>6.996289491653442</v>
       </c>
       <c r="J39" t="n">
-        <v>7.891449928283691</v>
+        <v>6.912514209747314</v>
       </c>
       <c r="K39" t="n">
-        <v>7.821060419082642</v>
+        <v>6.43878173828125</v>
       </c>
       <c r="L39" t="n">
-        <v>7.729724454879761</v>
+        <v>7.138188648223877</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>10.21152353286743</v>
+        <v>8.04909873008728</v>
       </c>
       <c r="C40" t="n">
-        <v>7.406116485595703</v>
+        <v>8.791489601135254</v>
       </c>
       <c r="D40" t="n">
-        <v>7.968240976333618</v>
+        <v>8.204151153564453</v>
       </c>
       <c r="E40" t="n">
-        <v>8.330300569534302</v>
+        <v>8.295935869216919</v>
       </c>
       <c r="F40" t="n">
-        <v>9.274842500686646</v>
+        <v>10.08380389213562</v>
       </c>
       <c r="G40" t="n">
-        <v>7.46497917175293</v>
+        <v>8.415494203567505</v>
       </c>
       <c r="H40" t="n">
-        <v>8.701341390609741</v>
+        <v>10.18775534629822</v>
       </c>
       <c r="I40" t="n">
-        <v>9.41306734085083</v>
+        <v>8.719681024551392</v>
       </c>
       <c r="J40" t="n">
-        <v>7.471462249755859</v>
+        <v>12.90869784355164</v>
       </c>
       <c r="K40" t="n">
-        <v>8.340229988098145</v>
+        <v>7.083059072494507</v>
       </c>
       <c r="L40" t="n">
-        <v>8.45821042060852</v>
+        <v>9.073916673660278</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>7.768197774887085</v>
+        <v>9.116620063781738</v>
       </c>
       <c r="C41" t="n">
-        <v>8.255960702896118</v>
+        <v>9.530513763427734</v>
       </c>
       <c r="D41" t="n">
-        <v>7.074968814849854</v>
+        <v>9.303120851516724</v>
       </c>
       <c r="E41" t="n">
-        <v>7.589183330535889</v>
+        <v>9.163495063781738</v>
       </c>
       <c r="F41" t="n">
-        <v>10.73815941810608</v>
+        <v>8.605230569839478</v>
       </c>
       <c r="G41" t="n">
-        <v>10.47484850883484</v>
+        <v>8.682214736938477</v>
       </c>
       <c r="H41" t="n">
-        <v>11.39300036430359</v>
+        <v>11.240238904953</v>
       </c>
       <c r="I41" t="n">
-        <v>9.688303470611572</v>
+        <v>8.295815229415894</v>
       </c>
       <c r="J41" t="n">
-        <v>7.700891256332397</v>
+        <v>9.803216457366943</v>
       </c>
       <c r="K41" t="n">
-        <v>7.414097309112549</v>
+        <v>7.8561110496521</v>
       </c>
       <c r="L41" t="n">
-        <v>8.809761095046998</v>
+        <v>9.159657669067382</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>6.031615495681763</v>
+        <v>7.522883176803589</v>
       </c>
       <c r="C42" t="n">
-        <v>5.871553659439087</v>
+        <v>6.319541931152344</v>
       </c>
       <c r="D42" t="n">
-        <v>5.984094142913818</v>
+        <v>8.734376430511475</v>
       </c>
       <c r="E42" t="n">
-        <v>6.587870359420776</v>
+        <v>6.124622106552124</v>
       </c>
       <c r="F42" t="n">
-        <v>6.427299976348877</v>
+        <v>6.195989370346069</v>
       </c>
       <c r="G42" t="n">
-        <v>8.225565910339355</v>
+        <v>6.562453269958496</v>
       </c>
       <c r="H42" t="n">
-        <v>8.207639217376709</v>
+        <v>5.963053226470947</v>
       </c>
       <c r="I42" t="n">
-        <v>5.904134511947632</v>
+        <v>6.190436124801636</v>
       </c>
       <c r="J42" t="n">
-        <v>7.390762567520142</v>
+        <v>6.145565509796143</v>
       </c>
       <c r="K42" t="n">
-        <v>5.840795278549194</v>
+        <v>6.515943050384521</v>
       </c>
       <c r="L42" t="n">
-        <v>6.647133111953735</v>
+        <v>6.627486419677735</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.883610010147095</v>
+        <v>6.67260479927063</v>
       </c>
       <c r="C43" t="n">
-        <v>6.651687383651733</v>
+        <v>6.376947164535522</v>
       </c>
       <c r="D43" t="n">
-        <v>9.744642734527588</v>
+        <v>8.56076455116272</v>
       </c>
       <c r="E43" t="n">
-        <v>6.855169773101807</v>
+        <v>7.129559755325317</v>
       </c>
       <c r="F43" t="n">
-        <v>8.673933744430542</v>
+        <v>8.544151544570923</v>
       </c>
       <c r="G43" t="n">
-        <v>8.161280155181885</v>
+        <v>6.995292663574219</v>
       </c>
       <c r="H43" t="n">
-        <v>10.26691484451294</v>
+        <v>7.930791854858398</v>
       </c>
       <c r="I43" t="n">
-        <v>6.496611356735229</v>
+        <v>8.265299320220947</v>
       </c>
       <c r="J43" t="n">
-        <v>8.699832677841187</v>
+        <v>9.132578134536743</v>
       </c>
       <c r="K43" t="n">
-        <v>8.289964437484741</v>
+        <v>8.781431913375854</v>
       </c>
       <c r="L43" t="n">
-        <v>8.072364711761475</v>
+        <v>7.838942170143127</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>9.289361715316772</v>
+        <v>6.730001449584961</v>
       </c>
       <c r="C44" t="n">
-        <v>7.232194900512695</v>
+        <v>8.759575128555298</v>
       </c>
       <c r="D44" t="n">
-        <v>6.962387084960938</v>
+        <v>7.053139448165894</v>
       </c>
       <c r="E44" t="n">
-        <v>6.809300661087036</v>
+        <v>7.701404333114624</v>
       </c>
       <c r="F44" t="n">
-        <v>6.764402151107788</v>
+        <v>7.017235040664673</v>
       </c>
       <c r="G44" t="n">
-        <v>6.898093461990356</v>
+        <v>7.827996730804443</v>
       </c>
       <c r="H44" t="n">
-        <v>7.766787767410278</v>
+        <v>7.695420742034912</v>
       </c>
       <c r="I44" t="n">
-        <v>8.058044672012329</v>
+        <v>8.117292881011963</v>
       </c>
       <c r="J44" t="n">
-        <v>7.475255012512207</v>
+        <v>6.953404426574707</v>
       </c>
       <c r="K44" t="n">
-        <v>7.131319046020508</v>
+        <v>8.181122303009033</v>
       </c>
       <c r="L44" t="n">
-        <v>7.438714647293091</v>
+        <v>7.60365924835205</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>6.865027666091919</v>
+        <v>7.556791067123413</v>
       </c>
       <c r="C45" t="n">
-        <v>7.69488263130188</v>
+        <v>9.850091218948364</v>
       </c>
       <c r="D45" t="n">
-        <v>7.700349569320679</v>
+        <v>12.6428918838501</v>
       </c>
       <c r="E45" t="n">
-        <v>7.182697534561157</v>
+        <v>8.182807445526123</v>
       </c>
       <c r="F45" t="n">
-        <v>7.41312313079834</v>
+        <v>9.505599021911621</v>
       </c>
       <c r="G45" t="n">
-        <v>7.014166116714478</v>
+        <v>9.372461318969727</v>
       </c>
       <c r="H45" t="n">
-        <v>9.371119022369385</v>
+        <v>7.763240098953247</v>
       </c>
       <c r="I45" t="n">
-        <v>7.771702527999878</v>
+        <v>12.07072043418884</v>
       </c>
       <c r="J45" t="n">
-        <v>8.346247434616089</v>
+        <v>9.072643041610718</v>
       </c>
       <c r="K45" t="n">
-        <v>9.7197425365448</v>
+        <v>9.491906404495239</v>
       </c>
       <c r="L45" t="n">
-        <v>7.90790581703186</v>
+        <v>9.550915193557739</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>7.727819919586182</v>
+        <v>6.866637468338013</v>
       </c>
       <c r="C46" t="n">
-        <v>8.892946481704712</v>
+        <v>7.444798707962036</v>
       </c>
       <c r="D46" t="n">
-        <v>9.015019416809082</v>
+        <v>8.764001131057739</v>
       </c>
       <c r="E46" t="n">
-        <v>9.427974224090576</v>
+        <v>9.329051971435547</v>
       </c>
       <c r="F46" t="n">
-        <v>10.01343369483948</v>
+        <v>12.95635342597961</v>
       </c>
       <c r="G46" t="n">
-        <v>9.359630584716797</v>
+        <v>11.01989221572876</v>
       </c>
       <c r="H46" t="n">
-        <v>6.828042507171631</v>
+        <v>7.377272129058838</v>
       </c>
       <c r="I46" t="n">
-        <v>10.11421513557434</v>
+        <v>6.994419574737549</v>
       </c>
       <c r="J46" t="n">
-        <v>7.538874864578247</v>
+        <v>7.676216602325439</v>
       </c>
       <c r="K46" t="n">
-        <v>8.396125555038452</v>
+        <v>7.997612476348877</v>
       </c>
       <c r="L46" t="n">
-        <v>8.73140823841095</v>
+        <v>8.642625570297241</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>8.264491319656372</v>
+        <v>8.867655754089355</v>
       </c>
       <c r="C47" t="n">
-        <v>10.32861685752869</v>
+        <v>8.209047555923462</v>
       </c>
       <c r="D47" t="n">
-        <v>8.676901340484619</v>
+        <v>7.95073676109314</v>
       </c>
       <c r="E47" t="n">
-        <v>9.256905078887939</v>
+        <v>10.40915369987488</v>
       </c>
       <c r="F47" t="n">
-        <v>9.56518292427063</v>
+        <v>9.0727379322052</v>
       </c>
       <c r="G47" t="n">
-        <v>9.111783981323242</v>
+        <v>7.37826943397522</v>
       </c>
       <c r="H47" t="n">
-        <v>7.180812120437622</v>
+        <v>9.329992055892944</v>
       </c>
       <c r="I47" t="n">
-        <v>7.097032308578491</v>
+        <v>8.604988098144531</v>
       </c>
       <c r="J47" t="n">
-        <v>9.938652276992798</v>
+        <v>9.562428712844849</v>
       </c>
       <c r="K47" t="n">
-        <v>8.683897495269775</v>
+        <v>8.62342643737793</v>
       </c>
       <c r="L47" t="n">
-        <v>8.810427570343018</v>
+        <v>8.800843644142152</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>8.091430187225342</v>
+        <v>6.9274742603302</v>
       </c>
       <c r="C48" t="n">
-        <v>9.455420970916748</v>
+        <v>7.010063648223877</v>
       </c>
       <c r="D48" t="n">
-        <v>10.07827639579773</v>
+        <v>7.900870800018311</v>
       </c>
       <c r="E48" t="n">
-        <v>6.750942468643188</v>
+        <v>6.099687576293945</v>
       </c>
       <c r="F48" t="n">
-        <v>7.209243297576904</v>
+        <v>8.800466537475586</v>
       </c>
       <c r="G48" t="n">
-        <v>6.500591278076172</v>
+        <v>6.536520004272461</v>
       </c>
       <c r="H48" t="n">
-        <v>9.744135618209839</v>
+        <v>6.538514614105225</v>
       </c>
       <c r="I48" t="n">
-        <v>6.579875230789185</v>
+        <v>8.767553567886353</v>
       </c>
       <c r="J48" t="n">
-        <v>7.430715322494507</v>
+        <v>7.924806833267212</v>
       </c>
       <c r="K48" t="n">
-        <v>7.085071325302124</v>
+        <v>6.572423934936523</v>
       </c>
       <c r="L48" t="n">
-        <v>7.892570209503174</v>
+        <v>7.307838177680969</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>10.43986892700195</v>
+        <v>7.358322143554688</v>
       </c>
       <c r="C49" t="n">
-        <v>7.820638418197632</v>
+        <v>9.563425302505493</v>
       </c>
       <c r="D49" t="n">
-        <v>10.03076529502869</v>
+        <v>8.203063011169434</v>
       </c>
       <c r="E49" t="n">
-        <v>9.480338335037231</v>
+        <v>9.228322267532349</v>
       </c>
       <c r="F49" t="n">
-        <v>8.872426509857178</v>
+        <v>7.254599332809448</v>
       </c>
       <c r="G49" t="n">
-        <v>10.29873085021973</v>
+        <v>7.237645149230957</v>
       </c>
       <c r="H49" t="n">
-        <v>9.100832939147949</v>
+        <v>7.900871276855469</v>
       </c>
       <c r="I49" t="n">
-        <v>8.150268316268921</v>
+        <v>7.856989145278931</v>
       </c>
       <c r="J49" t="n">
-        <v>6.963365793228149</v>
+        <v>14.13121008872986</v>
       </c>
       <c r="K49" t="n">
-        <v>8.891352891921997</v>
+        <v>7.479996204376221</v>
       </c>
       <c r="L49" t="n">
-        <v>9.004858827590942</v>
+        <v>8.621444392204285</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>10.08624482154846</v>
+        <v>8.764561891555786</v>
       </c>
       <c r="C50" t="n">
-        <v>8.350798368453979</v>
+        <v>8.492289543151855</v>
       </c>
       <c r="D50" t="n">
-        <v>9.268391132354736</v>
+        <v>7.478002548217773</v>
       </c>
       <c r="E50" t="n">
-        <v>7.043681383132935</v>
+        <v>6.979335308074951</v>
       </c>
       <c r="F50" t="n">
-        <v>8.234576463699341</v>
+        <v>7.011250257492065</v>
       </c>
       <c r="G50" t="n">
-        <v>10.38599562644958</v>
+        <v>7.39921236038208</v>
       </c>
       <c r="H50" t="n">
-        <v>9.41948938369751</v>
+        <v>7.575740575790405</v>
       </c>
       <c r="I50" t="n">
-        <v>7.024717569351196</v>
+        <v>7.137912034988403</v>
       </c>
       <c r="J50" t="n">
-        <v>8.886874675750732</v>
+        <v>7.358322381973267</v>
       </c>
       <c r="K50" t="n">
-        <v>10.29375457763672</v>
+        <v>6.965372562408447</v>
       </c>
       <c r="L50" t="n">
-        <v>8.899452400207519</v>
+        <v>7.516199946403503</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.039186954498291</v>
+        <v>9.652188539505005</v>
       </c>
       <c r="C51" t="n">
-        <v>9.510295867919922</v>
+        <v>8.475335597991943</v>
       </c>
       <c r="D51" t="n">
-        <v>8.642008781433105</v>
+        <v>7.059122323989868</v>
       </c>
       <c r="E51" t="n">
-        <v>8.565221071243286</v>
+        <v>10.28349995613098</v>
       </c>
       <c r="F51" t="n">
-        <v>7.684497117996216</v>
+        <v>7.75127124786377</v>
       </c>
       <c r="G51" t="n">
-        <v>8.551230430603027</v>
+        <v>8.616955995559692</v>
       </c>
       <c r="H51" t="n">
-        <v>8.881414651870728</v>
+        <v>8.167159080505371</v>
       </c>
       <c r="I51" t="n">
-        <v>8.027440071105957</v>
+        <v>7.42314887046814</v>
       </c>
       <c r="J51" t="n">
-        <v>10.25686550140381</v>
+        <v>8.17114782333374</v>
       </c>
       <c r="K51" t="n">
-        <v>6.571297645568848</v>
+        <v>8.735639572143555</v>
       </c>
       <c r="L51" t="n">
-        <v>8.372945809364319</v>
+        <v>8.433546900749207</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.401195797920227</v>
+        <v>8.075042004585265</v>
       </c>
       <c r="C52" t="n">
-        <v>7.985350761413574</v>
+        <v>8.140941052436828</v>
       </c>
       <c r="D52" t="n">
-        <v>8.244552297592163</v>
+        <v>8.230222816467284</v>
       </c>
       <c r="E52" t="n">
-        <v>8.054901366233826</v>
+        <v>8.301887693405151</v>
       </c>
       <c r="F52" t="n">
-        <v>8.167117347717285</v>
+        <v>8.527067213058471</v>
       </c>
       <c r="G52" t="n">
-        <v>8.108770766258239</v>
+        <v>8.286938991546631</v>
       </c>
       <c r="H52" t="n">
-        <v>8.293659682273864</v>
+        <v>8.006404504776</v>
       </c>
       <c r="I52" t="n">
-        <v>8.001897540092468</v>
+        <v>8.118928604125976</v>
       </c>
       <c r="J52" t="n">
-        <v>8.086776385307312</v>
+        <v>8.325906729698181</v>
       </c>
       <c r="K52" t="n">
-        <v>8.031878938674927</v>
+        <v>8.053854918479919</v>
       </c>
       <c r="L52" t="n">
-        <v>8.137610088348389</v>
+        <v>8.206719452857971</v>
       </c>
     </row>
   </sheetData>
